--- a/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/7_eight_bus_radial_grid_1ph_ynyn_MP_pf_sc_results_0_bus.xlsx
+++ b/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/7_eight_bus_radial_grid_1ph_ynyn_MP_pf_sc_results_0_bus.xlsx
@@ -68,10 +68,13 @@
     <t>pf_va_degree</t>
   </si>
   <si>
-    <t>Bus_0</t>
+    <t>Bus_1</t>
   </si>
   <si>
-    <t>Bus_1</t>
+    <t>Bus_5_3-1ph</t>
+  </si>
+  <si>
+    <t>Bus_6_3-1ph</t>
   </si>
   <si>
     <t>Bus_2_3-1ph</t>
@@ -80,16 +83,13 @@
     <t>Bus_3_3-1ph</t>
   </si>
   <si>
-    <t>Bus_4_3-1ph</t>
-  </si>
-  <si>
-    <t>Bus_5_3-1ph</t>
-  </si>
-  <si>
-    <t>Bus_6_3-1ph</t>
+    <t>Bus_0</t>
   </si>
   <si>
     <t>Bus_7_3-1ph</t>
+  </si>
+  <si>
+    <t>Bus_4_3-1ph</t>
   </si>
   <si>
     <t>pf_ikss_a_ka</t>
@@ -535,22 +535,22 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>2.886751509919007</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>100.0000056801178</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>0.4378163589895445</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>4.378163482065628</v>
+        <v>0</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>84.2894067227803</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -650,22 +650,22 @@
         <v>12</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>2.886751509919007</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>100.0000056801178</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>0.4378163589895445</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>4.378163482065628</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>84.2894067227803</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -785,66 +785,66 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>2.500000141999505</v>
+        <v>2.500000141999503</v>
       </c>
       <c r="D2">
-        <v>2.500000141999505</v>
+        <v>2.500000141999503</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>28.86751509915035</v>
+        <v>28.86751509915031</v>
       </c>
       <c r="G2">
-        <v>28.86751509915035</v>
+        <v>28.86751509915031</v>
       </c>
       <c r="H2">
-        <v>0.4394678541080421</v>
+        <v>0.4394678541080371</v>
       </c>
       <c r="I2">
-        <v>4.386313816163394</v>
+        <v>4.386313816163414</v>
       </c>
       <c r="J2">
-        <v>0.437816359016784</v>
+        <v>0.4378163590167802</v>
       </c>
       <c r="K2">
-        <v>4.378163482112572</v>
+        <v>4.378163482112585</v>
       </c>
       <c r="L2">
-        <v>0.4378163589897157</v>
+        <v>0.4378163589897112</v>
       </c>
       <c r="M2">
-        <v>4.378163482065464</v>
+        <v>4.378163482065474</v>
       </c>
       <c r="N2">
-        <v>0.9526279648091442</v>
+        <v>0.9526279648091471</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>0.9526279648092937</v>
+        <v>0.9526279648092969</v>
       </c>
       <c r="Q2">
-        <v>-6.054755891603807E-13</v>
+        <v>-6.479083724819258E-13</v>
       </c>
       <c r="R2">
         <v>0</v>
       </c>
       <c r="S2">
-        <v>179.999999999992</v>
+        <v>179.9999999999919</v>
       </c>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -883,27 +883,27 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9526279647466779</v>
+        <v>0.9526279647466808</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.9526279648717597</v>
+        <v>0.9526279648717636</v>
       </c>
       <c r="Q3">
-        <v>3.3106805189486E-09</v>
+        <v>3.310628640118341E-09</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
       <c r="S3">
-        <v>179.9999999966807</v>
+        <v>179.9999999966806</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -942,27 +942,27 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9526279647275288</v>
+        <v>0.9526279647275318</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.9526279648909088</v>
+        <v>0.9526279648909129</v>
       </c>
       <c r="Q4">
-        <v>5.639498082135461E-09</v>
+        <v>5.63943458093632E-09</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.9999999943519</v>
+        <v>179.9999999943518</v>
       </c>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1001,27 +1001,27 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9526279647275288</v>
+        <v>0.9526279647275316</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.9526279648909088</v>
+        <v>0.9526279648909128</v>
       </c>
       <c r="Q5">
-        <v>5.639498006993669E-09</v>
+        <v>5.639414410128948E-09</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9999999943519</v>
+        <v>179.9999999943518</v>
       </c>
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1060,27 +1060,27 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.9526279647275288</v>
+        <v>0.9526279647275316</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.9526279648909088</v>
+        <v>0.9526279648909127</v>
       </c>
       <c r="Q6">
-        <v>5.639498027382797E-09</v>
+        <v>5.63942687246306E-09</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>179.9999999943519</v>
+        <v>179.9999999943518</v>
       </c>
     </row>
     <row r="7" spans="1:19">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1119,27 +1119,27 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.9526279645354064</v>
+        <v>0.9526279645354094</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>0.952627965083031</v>
+        <v>0.9526279650830353</v>
       </c>
       <c r="Q7">
-        <v>6.800840012018049E-09</v>
+        <v>6.800776510818814E-09</v>
       </c>
       <c r="R7">
         <v>0</v>
       </c>
       <c r="S7">
-        <v>179.9999999931906</v>
+        <v>179.9999999931904</v>
       </c>
     </row>
     <row r="8" spans="1:19">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1178,27 +1178,27 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.9526279645354064</v>
+        <v>0.9526279645354094</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>0.952627965083031</v>
+        <v>0.9526279650830352</v>
       </c>
       <c r="Q8">
-        <v>6.800843792093914E-09</v>
+        <v>6.800752484793745E-09</v>
       </c>
       <c r="R8">
         <v>0</v>
       </c>
       <c r="S8">
-        <v>179.9999999931906</v>
+        <v>179.9999999931905</v>
       </c>
     </row>
     <row r="9" spans="1:19">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1237,22 +1237,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.9526279645354064</v>
+        <v>0.9526279645354094</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>0.952627965083031</v>
+        <v>0.9526279650830352</v>
       </c>
       <c r="Q9">
-        <v>6.80084381248304E-09</v>
+        <v>6.800764947127859E-09</v>
       </c>
       <c r="R9">
         <v>0</v>
       </c>
       <c r="S9">
-        <v>179.9999999931906</v>
+        <v>179.9999999931905</v>
       </c>
     </row>
   </sheetData>
@@ -1326,7 +1326,7 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1341,43 +1341,43 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>16.98248455947705</v>
+        <v>16.98248455947704</v>
       </c>
       <c r="G2">
-        <v>16.98248455947705</v>
+        <v>16.98248455947704</v>
       </c>
       <c r="H2">
-        <v>0.4394678541080287</v>
+        <v>0.4394678541080367</v>
       </c>
       <c r="I2">
-        <v>4.386313816163398</v>
+        <v>4.386313816163413</v>
       </c>
       <c r="J2">
-        <v>0.4378163590167708</v>
+        <v>0.4378163590167795</v>
       </c>
       <c r="K2">
-        <v>4.378163482112574</v>
+        <v>4.378163482112584</v>
       </c>
       <c r="L2">
-        <v>0.4378163589897015</v>
+        <v>0.4378163589897109</v>
       </c>
       <c r="M2">
-        <v>4.378163482065465</v>
+        <v>4.378163482065473</v>
       </c>
       <c r="N2">
-        <v>1.076859183429663</v>
+        <v>1.076859183429662</v>
       </c>
       <c r="O2">
-        <v>0.5199802716925331</v>
+        <v>0.5199802716925342</v>
       </c>
       <c r="P2">
-        <v>0.8891367269510999</v>
+        <v>0.8891367269511004</v>
       </c>
       <c r="Q2">
-        <v>12.9473495831839</v>
+        <v>12.94734958318391</v>
       </c>
       <c r="R2">
-        <v>-111.8715959827468</v>
+        <v>-111.8715959827467</v>
       </c>
       <c r="S2">
         <v>164.2547774329043</v>
@@ -1385,7 +1385,7 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1427,24 +1427,24 @@
         <v>1.076859183390501</v>
       </c>
       <c r="O3">
-        <v>0.5199802716961265</v>
+        <v>0.5199802716961279</v>
       </c>
       <c r="P3">
-        <v>0.8891367269995799</v>
+        <v>0.8891367269995802</v>
       </c>
       <c r="Q3">
-        <v>12.94734958474951</v>
+        <v>12.94734958474953</v>
       </c>
       <c r="R3">
-        <v>-111.8715959719592</v>
+        <v>-111.871595971959</v>
       </c>
       <c r="S3">
-        <v>164.2547774324526</v>
+        <v>164.2547774324525</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1486,24 +1486,24 @@
         <v>1.076859183377495</v>
       </c>
       <c r="O4">
-        <v>0.5199802717171188</v>
+        <v>0.5199802717171201</v>
       </c>
       <c r="P4">
-        <v>0.8891367270214707</v>
+        <v>0.889136727021471</v>
       </c>
       <c r="Q4">
-        <v>12.94734958591108</v>
+        <v>12.9473495859111</v>
       </c>
       <c r="R4">
-        <v>-111.8715959668589</v>
+        <v>-111.8715959668588</v>
       </c>
       <c r="S4">
-        <v>164.2547774316209</v>
+        <v>164.2547774316208</v>
       </c>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1542,27 +1542,27 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1.076859183377495</v>
+        <v>1.076859183377494</v>
       </c>
       <c r="O5">
-        <v>0.5199802717171187</v>
+        <v>0.51998027171712</v>
       </c>
       <c r="P5">
-        <v>0.8891367270214707</v>
+        <v>0.889136727021471</v>
       </c>
       <c r="Q5">
-        <v>12.94734958591107</v>
+        <v>12.94734958591109</v>
       </c>
       <c r="R5">
-        <v>-111.8715959668589</v>
+        <v>-111.8715959668588</v>
       </c>
       <c r="S5">
-        <v>164.2547774316209</v>
+        <v>164.2547774316208</v>
       </c>
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1604,16 +1604,16 @@
         <v>1.076859183377495</v>
       </c>
       <c r="O6">
-        <v>0.5199802717171188</v>
+        <v>0.51998027171712</v>
       </c>
       <c r="P6">
-        <v>0.8891367270214707</v>
+        <v>0.889136727021471</v>
       </c>
       <c r="Q6">
-        <v>12.94734958591107</v>
+        <v>12.94734958591109</v>
       </c>
       <c r="R6">
-        <v>-111.8715959668589</v>
+        <v>-111.8715959668588</v>
       </c>
       <c r="S6">
         <v>164.2547774316209</v>
@@ -1621,7 +1621,7 @@
     </row>
     <row r="7" spans="1:19">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1660,27 +1660,27 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>1.076859183269092</v>
+        <v>1.076859183269091</v>
       </c>
       <c r="O7">
-        <v>0.5199802715972675</v>
+        <v>0.5199802715972688</v>
       </c>
       <c r="P7">
-        <v>0.8891367271177155</v>
+        <v>0.8891367271177157</v>
       </c>
       <c r="Q7">
-        <v>12.94734958603881</v>
+        <v>12.94734958603884</v>
       </c>
       <c r="R7">
-        <v>-111.8715959469445</v>
+        <v>-111.8715959469443</v>
       </c>
       <c r="S7">
-        <v>164.254777434839</v>
+        <v>164.2547774348389</v>
       </c>
     </row>
     <row r="8" spans="1:19">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1719,27 +1719,27 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>1.076859183269092</v>
+        <v>1.076859183269091</v>
       </c>
       <c r="O8">
-        <v>0.5199802715972675</v>
+        <v>0.5199802715972688</v>
       </c>
       <c r="P8">
-        <v>0.8891367271177155</v>
+        <v>0.8891367271177159</v>
       </c>
       <c r="Q8">
-        <v>12.94734958603881</v>
+        <v>12.94734958603883</v>
       </c>
       <c r="R8">
-        <v>-111.8715959469445</v>
+        <v>-111.8715959469443</v>
       </c>
       <c r="S8">
-        <v>164.254777434839</v>
+        <v>164.2547774348389</v>
       </c>
     </row>
     <row r="9" spans="1:19">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1778,22 +1778,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>1.076859183269092</v>
+        <v>1.076859183269091</v>
       </c>
       <c r="O9">
-        <v>0.5199802715972675</v>
+        <v>0.5199802715972688</v>
       </c>
       <c r="P9">
-        <v>0.8891367271177155</v>
+        <v>0.8891367271177157</v>
       </c>
       <c r="Q9">
-        <v>12.94734958603881</v>
+        <v>12.94734958603883</v>
       </c>
       <c r="R9">
-        <v>-111.8715959469445</v>
+        <v>-111.8715959469443</v>
       </c>
       <c r="S9">
-        <v>164.254777434839</v>
+        <v>164.2547774348389</v>
       </c>
     </row>
   </sheetData>
@@ -1867,66 +1867,66 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>1.47072630478841</v>
+        <v>1.470726304788408</v>
       </c>
       <c r="D2">
-        <v>1.47072630478841</v>
+        <v>1.470726304788408</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>16.98248455947704</v>
+        <v>16.98248455947702</v>
       </c>
       <c r="G2">
-        <v>16.98248455947704</v>
+        <v>16.98248455947702</v>
       </c>
       <c r="H2">
-        <v>0.4394678541080421</v>
+        <v>0.4394678541080371</v>
       </c>
       <c r="I2">
-        <v>4.386313816163394</v>
+        <v>4.386313816163414</v>
       </c>
       <c r="J2">
-        <v>0.437816359016784</v>
+        <v>0.4378163590167802</v>
       </c>
       <c r="K2">
-        <v>4.378163482112572</v>
+        <v>4.378163482112585</v>
       </c>
       <c r="L2">
-        <v>0.4378163589897157</v>
+        <v>0.4378163589897112</v>
       </c>
       <c r="M2">
-        <v>4.378163482065464</v>
+        <v>4.378163482065474</v>
       </c>
       <c r="N2">
         <v>1.076859183429662</v>
       </c>
       <c r="O2">
-        <v>0.519980271692534</v>
+        <v>0.5199802716925349</v>
       </c>
       <c r="P2">
-        <v>0.8891367269510991</v>
+        <v>0.8891367269511016</v>
       </c>
       <c r="Q2">
-        <v>12.94734958318394</v>
+        <v>12.94734958318391</v>
       </c>
       <c r="R2">
-        <v>-111.8715959827468</v>
+        <v>-111.8715959827466</v>
       </c>
       <c r="S2">
-        <v>164.2547774329043</v>
+        <v>164.2547774329042</v>
       </c>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1968,24 +1968,24 @@
         <v>1.076859183390501</v>
       </c>
       <c r="O3">
-        <v>0.5199802716961275</v>
+        <v>0.5199802716961285</v>
       </c>
       <c r="P3">
-        <v>0.8891367269995787</v>
+        <v>0.8891367269995817</v>
       </c>
       <c r="Q3">
-        <v>12.94734958474957</v>
+        <v>12.94734958474953</v>
       </c>
       <c r="R3">
-        <v>-111.8715959719591</v>
+        <v>-111.8715959719589</v>
       </c>
       <c r="S3">
-        <v>164.2547774324525</v>
+        <v>164.2547774324524</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2027,24 +2027,24 @@
         <v>1.076859183377495</v>
       </c>
       <c r="O4">
-        <v>0.5199802717171197</v>
+        <v>0.5199802717171206</v>
       </c>
       <c r="P4">
-        <v>0.8891367270214695</v>
+        <v>0.8891367270214725</v>
       </c>
       <c r="Q4">
-        <v>12.94734958591112</v>
+        <v>12.94734958591109</v>
       </c>
       <c r="R4">
-        <v>-111.8715959668589</v>
+        <v>-111.8715959668587</v>
       </c>
       <c r="S4">
-        <v>164.2547774316209</v>
+        <v>164.2547774316208</v>
       </c>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2083,27 +2083,27 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1.076859183377494</v>
+        <v>1.076859183377495</v>
       </c>
       <c r="O5">
-        <v>0.5199802717171197</v>
+        <v>0.5199802717171206</v>
       </c>
       <c r="P5">
-        <v>0.8891367270214695</v>
+        <v>0.8891367270214725</v>
       </c>
       <c r="Q5">
-        <v>12.94734958591113</v>
+        <v>12.94734958591109</v>
       </c>
       <c r="R5">
-        <v>-111.8715959668589</v>
+        <v>-111.8715959668587</v>
       </c>
       <c r="S5">
-        <v>164.2547774316209</v>
+        <v>164.2547774316208</v>
       </c>
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2142,27 +2142,27 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>1.076859183377494</v>
+        <v>1.076859183377495</v>
       </c>
       <c r="O6">
-        <v>0.5199802717171197</v>
+        <v>0.5199802717171205</v>
       </c>
       <c r="P6">
-        <v>0.8891367270214695</v>
+        <v>0.8891367270214725</v>
       </c>
       <c r="Q6">
-        <v>12.94734958591113</v>
+        <v>12.94734958591109</v>
       </c>
       <c r="R6">
-        <v>-111.8715959668589</v>
+        <v>-111.8715959668587</v>
       </c>
       <c r="S6">
-        <v>164.2547774316209</v>
+        <v>164.2547774316208</v>
       </c>
     </row>
     <row r="7" spans="1:19">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2201,27 +2201,27 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>1.076859183263929</v>
+        <v>1.07685918326393</v>
       </c>
       <c r="O7">
-        <v>0.5199802715915609</v>
+        <v>0.519980271591562</v>
       </c>
       <c r="P7">
-        <v>0.8891367271222974</v>
+        <v>0.8891367271223003</v>
       </c>
       <c r="Q7">
-        <v>12.94734958604494</v>
+        <v>12.94734958604491</v>
       </c>
       <c r="R7">
-        <v>-111.8715959459962</v>
+        <v>-111.8715959459959</v>
       </c>
       <c r="S7">
-        <v>164.2547774349922</v>
+        <v>164.2547774349921</v>
       </c>
     </row>
     <row r="8" spans="1:19">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2260,27 +2260,27 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>1.076859183263929</v>
+        <v>1.07685918326393</v>
       </c>
       <c r="O8">
-        <v>0.5199802715915612</v>
+        <v>0.519980271591562</v>
       </c>
       <c r="P8">
-        <v>0.8891367271222975</v>
+        <v>0.8891367271223002</v>
       </c>
       <c r="Q8">
-        <v>12.94734958604495</v>
+        <v>12.94734958604491</v>
       </c>
       <c r="R8">
-        <v>-111.8715959459962</v>
+        <v>-111.8715959459959</v>
       </c>
       <c r="S8">
-        <v>164.2547774349922</v>
+        <v>164.2547774349921</v>
       </c>
     </row>
     <row r="9" spans="1:19">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2319,22 +2319,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>1.076859183263929</v>
+        <v>1.07685918326393</v>
       </c>
       <c r="O9">
-        <v>0.5199802715915611</v>
+        <v>0.5199802715915619</v>
       </c>
       <c r="P9">
-        <v>0.8891367271222975</v>
+        <v>0.8891367271223002</v>
       </c>
       <c r="Q9">
-        <v>12.94734958604495</v>
+        <v>12.9473495860449</v>
       </c>
       <c r="R9">
-        <v>-111.8715959459961</v>
+        <v>-111.8715959459959</v>
       </c>
       <c r="S9">
-        <v>164.2547774349922</v>
+        <v>164.2547774349921</v>
       </c>
     </row>
   </sheetData>
@@ -2408,55 +2408,55 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>2.000000070285387</v>
+        <v>2.000000070285388</v>
       </c>
       <c r="D2">
-        <v>2.000000070285387</v>
+        <v>2.000000070285388</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>23.09401157917077</v>
+        <v>23.09401157917079</v>
       </c>
       <c r="G2">
-        <v>23.09401157917077</v>
+        <v>23.09401157917079</v>
       </c>
       <c r="H2">
-        <v>0.499655865049651</v>
+        <v>0.4996558650496533</v>
       </c>
       <c r="I2">
-        <v>4.985712340298376</v>
+        <v>4.985712340298373</v>
       </c>
       <c r="J2">
-        <v>0.497518590390245</v>
+        <v>0.4975185903902516</v>
       </c>
       <c r="K2">
-        <v>4.975185774913276</v>
+        <v>4.975185774913275</v>
       </c>
       <c r="L2">
-        <v>0.4975185904079639</v>
+        <v>0.4975185904079694</v>
       </c>
       <c r="M2">
-        <v>4.975185774943705</v>
+        <v>4.975185774943702</v>
       </c>
       <c r="N2">
-        <v>0.8660254037872088</v>
+        <v>0.8660254037872067</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>0.8660254037869275</v>
+        <v>0.8660254037869252</v>
       </c>
       <c r="Q2">
-        <v>7.433467529403639E-12</v>
+        <v>7.436152164843258E-12</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -2467,7 +2467,7 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2506,27 +2506,27 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8660254037304213</v>
+        <v>0.8660254037304191</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.8660254038437151</v>
+        <v>0.8660254038437126</v>
       </c>
       <c r="Q3">
-        <v>6.365087918414097E-09</v>
+        <v>6.365118194161914E-09</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
       <c r="S3">
-        <v>179.9999999936262</v>
+        <v>179.9999999936263</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2565,27 +2565,27 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8660254037130128</v>
+        <v>0.8660254037130107</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.8660254038611234</v>
+        <v>0.8660254038611209</v>
       </c>
       <c r="Q4">
-        <v>1.083640896285994E-08</v>
+        <v>1.083646194726124E-08</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.9999999891549</v>
+        <v>179.999999989155</v>
       </c>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2624,27 +2624,27 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8660254037130128</v>
+        <v>0.8660254037130107</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.8660254038611234</v>
+        <v>0.8660254038611209</v>
       </c>
       <c r="Q5">
-        <v>1.083640926130021E-08</v>
+        <v>1.083644212996181E-08</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9999999891549</v>
+        <v>179.999999989155</v>
       </c>
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2683,27 +2683,27 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.8660254037130128</v>
+        <v>0.8660254037130107</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.8660254038611234</v>
+        <v>0.8660254038611209</v>
       </c>
       <c r="Q6">
-        <v>1.083640922711818E-08</v>
+        <v>1.083643950286806E-08</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>179.9999999891549</v>
+        <v>179.999999989155</v>
       </c>
     </row>
     <row r="7" spans="1:19">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2742,16 +2742,16 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.866025403537895</v>
+        <v>0.8660254035378929</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>0.8660254040362412</v>
+        <v>0.8660254040362387</v>
       </c>
       <c r="Q7">
-        <v>1.200081003422567E-08</v>
+        <v>1.20008630186271E-08</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -2762,7 +2762,7 @@
     </row>
     <row r="8" spans="1:19">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2801,16 +2801,16 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.866025403537895</v>
+        <v>0.8660254035378929</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>0.8660254040362412</v>
+        <v>0.8660254040362387</v>
       </c>
       <c r="Q8">
-        <v>1.200081457340551E-08</v>
+        <v>1.200084744206724E-08</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -2821,7 +2821,7 @@
     </row>
     <row r="9" spans="1:19">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2860,16 +2860,16 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.866025403537895</v>
+        <v>0.8660254035378929</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>0.8660254040362412</v>
+        <v>0.8660254040362387</v>
       </c>
       <c r="Q9">
-        <v>1.200081453922348E-08</v>
+        <v>1.200084481497349E-08</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -2949,55 +2949,55 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>2.000000070285387</v>
+        <v>2.000000070285388</v>
       </c>
       <c r="D2">
-        <v>2.000000070285387</v>
+        <v>2.000000070285388</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>23.09401157917077</v>
+        <v>23.09401157917079</v>
       </c>
       <c r="G2">
-        <v>23.09401157917077</v>
+        <v>23.09401157917079</v>
       </c>
       <c r="H2">
-        <v>0.499655865049651</v>
+        <v>0.4996558650496533</v>
       </c>
       <c r="I2">
-        <v>4.985712340298376</v>
+        <v>4.985712340298373</v>
       </c>
       <c r="J2">
-        <v>0.497518590390245</v>
+        <v>0.4975185903902516</v>
       </c>
       <c r="K2">
-        <v>4.975185774913276</v>
+        <v>4.975185774913275</v>
       </c>
       <c r="L2">
-        <v>0.4975185904079639</v>
+        <v>0.4975185904079694</v>
       </c>
       <c r="M2">
-        <v>4.975185774943705</v>
+        <v>4.975185774943702</v>
       </c>
       <c r="N2">
-        <v>0.8660254037872088</v>
+        <v>0.8660254037872067</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>0.8660254037869275</v>
+        <v>0.8660254037869252</v>
       </c>
       <c r="Q2">
-        <v>7.433467529403639E-12</v>
+        <v>7.436152164843258E-12</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -3008,7 +3008,7 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -3047,27 +3047,27 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8660254037304213</v>
+        <v>0.8660254037304191</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.8660254038437151</v>
+        <v>0.8660254038437126</v>
       </c>
       <c r="Q3">
-        <v>6.365087918414097E-09</v>
+        <v>6.365118194161914E-09</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
       <c r="S3">
-        <v>179.9999999936262</v>
+        <v>179.9999999936263</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -3106,27 +3106,27 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8660254037130128</v>
+        <v>0.8660254037130107</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.8660254038611234</v>
+        <v>0.8660254038611209</v>
       </c>
       <c r="Q4">
-        <v>1.083640896285994E-08</v>
+        <v>1.083646194726124E-08</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.9999999891549</v>
+        <v>179.999999989155</v>
       </c>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -3165,27 +3165,27 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8660254037130128</v>
+        <v>0.8660254037130107</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.8660254038611234</v>
+        <v>0.8660254038611209</v>
       </c>
       <c r="Q5">
-        <v>1.083640926130021E-08</v>
+        <v>1.083644212996181E-08</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9999999891549</v>
+        <v>179.999999989155</v>
       </c>
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -3224,27 +3224,27 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.8660254037130128</v>
+        <v>0.8660254037130107</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.8660254038611234</v>
+        <v>0.8660254038611209</v>
       </c>
       <c r="Q6">
-        <v>1.083640922711818E-08</v>
+        <v>1.083643950286806E-08</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>179.9999999891549</v>
+        <v>179.999999989155</v>
       </c>
     </row>
     <row r="7" spans="1:19">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -3283,16 +3283,16 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.866025403537895</v>
+        <v>0.8660254035378929</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>0.8660254040362412</v>
+        <v>0.8660254040362387</v>
       </c>
       <c r="Q7">
-        <v>1.200081003422567E-08</v>
+        <v>1.20008630186271E-08</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -3303,7 +3303,7 @@
     </row>
     <row r="8" spans="1:19">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -3342,16 +3342,16 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.866025403537895</v>
+        <v>0.8660254035378929</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>0.8660254040362412</v>
+        <v>0.8660254040362387</v>
       </c>
       <c r="Q8">
-        <v>1.200081457340551E-08</v>
+        <v>1.200084744206724E-08</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -3362,7 +3362,7 @@
     </row>
     <row r="9" spans="1:19">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -3401,16 +3401,16 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.866025403537895</v>
+        <v>0.8660254035378929</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>0.8660254040362412</v>
+        <v>0.8660254040362387</v>
       </c>
       <c r="Q9">
-        <v>1.200081453922348E-08</v>
+        <v>1.200084481497349E-08</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -3490,66 +3490,66 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>1.241651573334927</v>
+        <v>1.241651573334928</v>
       </c>
       <c r="D2">
-        <v>1.241651573334927</v>
+        <v>1.241651573334928</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>14.33735740209285</v>
+        <v>14.33735740209286</v>
       </c>
       <c r="G2">
-        <v>14.33735740209285</v>
+        <v>14.33735740209286</v>
       </c>
       <c r="H2">
-        <v>0.499655865049651</v>
+        <v>0.4996558650496533</v>
       </c>
       <c r="I2">
-        <v>4.985712340298376</v>
+        <v>4.985712340298373</v>
       </c>
       <c r="J2">
-        <v>0.497518590390245</v>
+        <v>0.4975185903902516</v>
       </c>
       <c r="K2">
-        <v>4.975185774913276</v>
+        <v>4.975185774913275</v>
       </c>
       <c r="L2">
-        <v>0.4975185904079639</v>
+        <v>0.4975185904079694</v>
       </c>
       <c r="M2">
-        <v>4.975185774943705</v>
+        <v>4.975185774943702</v>
       </c>
       <c r="N2">
-        <v>0.9734665046418941</v>
+        <v>0.9734665046418931</v>
       </c>
       <c r="O2">
-        <v>0.4389901236888178</v>
+        <v>0.4389901236888182</v>
       </c>
       <c r="P2">
-        <v>0.8054310204449506</v>
+        <v>0.8054310204449493</v>
       </c>
       <c r="Q2">
-        <v>11.96551486252557</v>
+        <v>11.96551486252558</v>
       </c>
       <c r="R2">
         <v>-113.149418707693</v>
       </c>
       <c r="S2">
-        <v>165.4883827687182</v>
+        <v>165.4883827687181</v>
       </c>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -3588,27 +3588,27 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9734665046023897</v>
+        <v>0.9734665046023885</v>
       </c>
       <c r="O3">
-        <v>0.4389901237365149</v>
+        <v>0.4389901237365154</v>
       </c>
       <c r="P3">
-        <v>0.8054310205056953</v>
+        <v>0.8054310205056934</v>
       </c>
       <c r="Q3">
-        <v>11.96551486587657</v>
+        <v>11.9655148658766</v>
       </c>
       <c r="R3">
-        <v>-113.149418690709</v>
+        <v>-113.1494186907091</v>
       </c>
       <c r="S3">
-        <v>165.4883827663458</v>
+        <v>165.4883827663457</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -3647,19 +3647,19 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9734665045885565</v>
+        <v>0.9734665045885553</v>
       </c>
       <c r="O4">
-        <v>0.4389901237877747</v>
+        <v>0.4389901237877752</v>
       </c>
       <c r="P4">
-        <v>0.8054310205363837</v>
+        <v>0.8054310205363816</v>
       </c>
       <c r="Q4">
-        <v>11.96551486829325</v>
+        <v>11.96551486829329</v>
       </c>
       <c r="R4">
-        <v>-113.14941868159</v>
+        <v>-113.1494186815901</v>
       </c>
       <c r="S4">
         <v>165.48838276417</v>
@@ -3667,7 +3667,7 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -3706,19 +3706,19 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9734665045885564</v>
+        <v>0.9734665045885553</v>
       </c>
       <c r="O5">
-        <v>0.4389901237877747</v>
+        <v>0.4389901237877751</v>
       </c>
       <c r="P5">
-        <v>0.8054310205363837</v>
+        <v>0.8054310205363816</v>
       </c>
       <c r="Q5">
-        <v>11.96551486829325</v>
+        <v>11.96551486829328</v>
       </c>
       <c r="R5">
-        <v>-113.14941868159</v>
+        <v>-113.1494186815901</v>
       </c>
       <c r="S5">
         <v>165.48838276417</v>
@@ -3726,7 +3726,7 @@
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -3765,19 +3765,19 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.9734665045885565</v>
+        <v>0.9734665045885553</v>
       </c>
       <c r="O6">
-        <v>0.4389901237877747</v>
+        <v>0.4389901237877751</v>
       </c>
       <c r="P6">
-        <v>0.8054310205363837</v>
+        <v>0.8054310205363816</v>
       </c>
       <c r="Q6">
-        <v>11.96551486829325</v>
+        <v>11.96551486829328</v>
       </c>
       <c r="R6">
-        <v>-113.14941868159</v>
+        <v>-113.1494186815901</v>
       </c>
       <c r="S6">
         <v>165.48838276417</v>
@@ -3785,7 +3785,7 @@
     </row>
     <row r="7" spans="1:19">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -3824,19 +3824,19 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.973466504479332</v>
+        <v>0.9734665044793308</v>
       </c>
       <c r="O7">
-        <v>0.4389901236669997</v>
+        <v>0.4389901236670002</v>
       </c>
       <c r="P7">
-        <v>0.8054310206354822</v>
+        <v>0.8054310206354801</v>
       </c>
       <c r="Q7">
-        <v>11.96551486846885</v>
+        <v>11.9655148684689</v>
       </c>
       <c r="R7">
-        <v>-113.1494186578197</v>
+        <v>-113.1494186578198</v>
       </c>
       <c r="S7">
         <v>165.4883827674441</v>
@@ -3844,7 +3844,7 @@
     </row>
     <row r="8" spans="1:19">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -3883,19 +3883,19 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.9734665044793318</v>
+        <v>0.9734665044793308</v>
       </c>
       <c r="O8">
-        <v>0.4389901236669997</v>
+        <v>0.4389901236670001</v>
       </c>
       <c r="P8">
-        <v>0.805431020635482</v>
+        <v>0.8054310206354801</v>
       </c>
       <c r="Q8">
-        <v>11.96551486846886</v>
+        <v>11.96551486846888</v>
       </c>
       <c r="R8">
-        <v>-113.1494186578197</v>
+        <v>-113.1494186578198</v>
       </c>
       <c r="S8">
         <v>165.4883827674441</v>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="9" spans="1:19">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -3942,19 +3942,19 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.973466504479332</v>
+        <v>0.9734665044793307</v>
       </c>
       <c r="O9">
-        <v>0.4389901236669997</v>
+        <v>0.4389901236670001</v>
       </c>
       <c r="P9">
-        <v>0.8054310206354822</v>
+        <v>0.8054310206354801</v>
       </c>
       <c r="Q9">
-        <v>11.96551486846885</v>
+        <v>11.96551486846888</v>
       </c>
       <c r="R9">
-        <v>-113.1494186578197</v>
+        <v>-113.1494186578198</v>
       </c>
       <c r="S9">
         <v>165.4883827674441</v>
@@ -4031,66 +4031,66 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>1.241651573334927</v>
+        <v>1.241651573334928</v>
       </c>
       <c r="D2">
-        <v>1.241651573334927</v>
+        <v>1.241651573334928</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>14.33735740209285</v>
+        <v>14.33735740209286</v>
       </c>
       <c r="G2">
-        <v>14.33735740209285</v>
+        <v>14.33735740209286</v>
       </c>
       <c r="H2">
-        <v>0.499655865049651</v>
+        <v>0.4996558650496533</v>
       </c>
       <c r="I2">
-        <v>4.985712340298376</v>
+        <v>4.985712340298373</v>
       </c>
       <c r="J2">
-        <v>0.497518590390245</v>
+        <v>0.4975185903902516</v>
       </c>
       <c r="K2">
-        <v>4.975185774913276</v>
+        <v>4.975185774913275</v>
       </c>
       <c r="L2">
-        <v>0.4975185904079639</v>
+        <v>0.4975185904079694</v>
       </c>
       <c r="M2">
-        <v>4.975185774943705</v>
+        <v>4.975185774943702</v>
       </c>
       <c r="N2">
-        <v>0.9734665046418941</v>
+        <v>0.9734665046418931</v>
       </c>
       <c r="O2">
-        <v>0.4389901236888178</v>
+        <v>0.4389901236888182</v>
       </c>
       <c r="P2">
-        <v>0.8054310204449506</v>
+        <v>0.8054310204449493</v>
       </c>
       <c r="Q2">
-        <v>11.96551486252557</v>
+        <v>11.96551486252558</v>
       </c>
       <c r="R2">
         <v>-113.149418707693</v>
       </c>
       <c r="S2">
-        <v>165.4883827687182</v>
+        <v>165.4883827687181</v>
       </c>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -4129,27 +4129,27 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9734665046023897</v>
+        <v>0.9734665046023885</v>
       </c>
       <c r="O3">
-        <v>0.4389901237365149</v>
+        <v>0.4389901237365154</v>
       </c>
       <c r="P3">
-        <v>0.8054310205056953</v>
+        <v>0.8054310205056934</v>
       </c>
       <c r="Q3">
-        <v>11.96551486587657</v>
+        <v>11.9655148658766</v>
       </c>
       <c r="R3">
-        <v>-113.149418690709</v>
+        <v>-113.1494186907091</v>
       </c>
       <c r="S3">
-        <v>165.4883827663458</v>
+        <v>165.4883827663457</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -4188,19 +4188,19 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9734665045885565</v>
+        <v>0.9734665045885553</v>
       </c>
       <c r="O4">
-        <v>0.4389901237877747</v>
+        <v>0.4389901237877752</v>
       </c>
       <c r="P4">
-        <v>0.8054310205363837</v>
+        <v>0.8054310205363816</v>
       </c>
       <c r="Q4">
-        <v>11.96551486829325</v>
+        <v>11.96551486829329</v>
       </c>
       <c r="R4">
-        <v>-113.14941868159</v>
+        <v>-113.1494186815901</v>
       </c>
       <c r="S4">
         <v>165.48838276417</v>
@@ -4208,7 +4208,7 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -4247,19 +4247,19 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9734665045885564</v>
+        <v>0.9734665045885553</v>
       </c>
       <c r="O5">
-        <v>0.4389901237877747</v>
+        <v>0.4389901237877751</v>
       </c>
       <c r="P5">
-        <v>0.8054310205363837</v>
+        <v>0.8054310205363816</v>
       </c>
       <c r="Q5">
-        <v>11.96551486829325</v>
+        <v>11.96551486829328</v>
       </c>
       <c r="R5">
-        <v>-113.14941868159</v>
+        <v>-113.1494186815901</v>
       </c>
       <c r="S5">
         <v>165.48838276417</v>
@@ -4267,7 +4267,7 @@
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -4306,19 +4306,19 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.9734665045885565</v>
+        <v>0.9734665045885553</v>
       </c>
       <c r="O6">
-        <v>0.4389901237877747</v>
+        <v>0.4389901237877751</v>
       </c>
       <c r="P6">
-        <v>0.8054310205363837</v>
+        <v>0.8054310205363816</v>
       </c>
       <c r="Q6">
-        <v>11.96551486829325</v>
+        <v>11.96551486829328</v>
       </c>
       <c r="R6">
-        <v>-113.14941868159</v>
+        <v>-113.1494186815901</v>
       </c>
       <c r="S6">
         <v>165.48838276417</v>
@@ -4326,7 +4326,7 @@
     </row>
     <row r="7" spans="1:19">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -4365,19 +4365,19 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.973466504479332</v>
+        <v>0.9734665044793308</v>
       </c>
       <c r="O7">
-        <v>0.4389901236669997</v>
+        <v>0.4389901236670002</v>
       </c>
       <c r="P7">
-        <v>0.8054310206354822</v>
+        <v>0.8054310206354801</v>
       </c>
       <c r="Q7">
-        <v>11.96551486846885</v>
+        <v>11.9655148684689</v>
       </c>
       <c r="R7">
-        <v>-113.1494186578197</v>
+        <v>-113.1494186578198</v>
       </c>
       <c r="S7">
         <v>165.4883827674441</v>
@@ -4385,7 +4385,7 @@
     </row>
     <row r="8" spans="1:19">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -4424,19 +4424,19 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.9734665044793318</v>
+        <v>0.9734665044793308</v>
       </c>
       <c r="O8">
-        <v>0.4389901236669997</v>
+        <v>0.4389901236670001</v>
       </c>
       <c r="P8">
-        <v>0.805431020635482</v>
+        <v>0.8054310206354801</v>
       </c>
       <c r="Q8">
-        <v>11.96551486846886</v>
+        <v>11.96551486846888</v>
       </c>
       <c r="R8">
-        <v>-113.1494186578197</v>
+        <v>-113.1494186578198</v>
       </c>
       <c r="S8">
         <v>165.4883827674441</v>
@@ -4444,7 +4444,7 @@
     </row>
     <row r="9" spans="1:19">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -4483,19 +4483,19 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.973466504479332</v>
+        <v>0.9734665044793307</v>
       </c>
       <c r="O9">
-        <v>0.4389901236669997</v>
+        <v>0.4389901236670001</v>
       </c>
       <c r="P9">
-        <v>0.8054310206354822</v>
+        <v>0.8054310206354801</v>
       </c>
       <c r="Q9">
-        <v>11.96551486846885</v>
+        <v>11.96551486846888</v>
       </c>
       <c r="R9">
-        <v>-113.1494186578197</v>
+        <v>-113.1494186578198</v>
       </c>
       <c r="S9">
         <v>165.4883827674441</v>
@@ -4575,10 +4575,10 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B2">
-        <v>2.884943122233678</v>
+        <v>2.884943122233679</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -4587,7 +4587,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>33.31245376436747</v>
+        <v>33.31245376436748</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -4596,40 +4596,40 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0.4394678541080387</v>
+        <v>0.4394678541080334</v>
       </c>
       <c r="I2">
-        <v>4.386313816163039</v>
+        <v>4.386313816163042</v>
       </c>
       <c r="J2">
-        <v>0.4378163590117159</v>
+        <v>0.4378163590117204</v>
       </c>
       <c r="K2">
-        <v>4.378163482065635</v>
+        <v>4.378163482065638</v>
       </c>
       <c r="L2">
-        <v>0.4378163589897304</v>
+        <v>0.437816358989736</v>
       </c>
       <c r="M2">
-        <v>4.378163482065387</v>
+        <v>4.378163482065375</v>
       </c>
       <c r="N2">
-        <v>0.6352497015657879</v>
+        <v>0.6352497015657916</v>
       </c>
       <c r="O2">
         <v>1.100000023837896</v>
       </c>
       <c r="P2">
-        <v>0.635318952205696</v>
+        <v>0.6353189522056928</v>
       </c>
       <c r="Q2">
-        <v>59.96712042125113</v>
+        <v>59.96712042125129</v>
       </c>
       <c r="R2">
         <v>-89.99999999999636</v>
       </c>
       <c r="S2">
-        <v>120.0292691278698</v>
+        <v>120.02926912787</v>
       </c>
       <c r="T2">
         <v>2.884943122233678</v>
@@ -4637,7 +4637,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -4676,22 +4676,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.6352497016599931</v>
+        <v>0.6352497016599975</v>
       </c>
       <c r="O3">
         <v>1.100000023837896</v>
       </c>
       <c r="P3">
-        <v>0.6353189521750761</v>
+        <v>0.6353189521750726</v>
       </c>
       <c r="Q3">
-        <v>59.9671204195448</v>
+        <v>59.96712041954495</v>
       </c>
       <c r="R3">
         <v>-89.99999999999636</v>
       </c>
       <c r="S3">
-        <v>120.0292691360835</v>
+        <v>120.0292691360837</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -4699,7 +4699,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -4738,22 +4738,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.635249701701489</v>
+        <v>0.6352497017014933</v>
       </c>
       <c r="O4">
         <v>1.100000023837896</v>
       </c>
       <c r="P4">
-        <v>0.6353189521783021</v>
+        <v>0.6353189521782988</v>
       </c>
       <c r="Q4">
-        <v>59.96712041705359</v>
+        <v>59.96712041705374</v>
       </c>
       <c r="R4">
         <v>-89.99999999999636</v>
       </c>
       <c r="S4">
-        <v>120.0292691405695</v>
+        <v>120.0292691405698</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -4761,7 +4761,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -4800,22 +4800,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.635249701701489</v>
+        <v>0.6352497017014934</v>
       </c>
       <c r="O5">
         <v>1.100000023837896</v>
       </c>
       <c r="P5">
-        <v>0.6353189521783021</v>
+        <v>0.6353189521782988</v>
       </c>
       <c r="Q5">
-        <v>59.96712041705359</v>
+        <v>59.96712041705373</v>
       </c>
       <c r="R5">
         <v>-89.99999999999636</v>
       </c>
       <c r="S5">
-        <v>120.0292691405695</v>
+        <v>120.0292691405698</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -4823,7 +4823,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -4862,22 +4862,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.635249701701489</v>
+        <v>0.6352497017014933</v>
       </c>
       <c r="O6">
         <v>1.100000023837896</v>
       </c>
       <c r="P6">
-        <v>0.635318952178302</v>
+        <v>0.6353189521782988</v>
       </c>
       <c r="Q6">
-        <v>59.9671204170536</v>
+        <v>59.96712041705374</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999636</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S6">
-        <v>120.0292691405695</v>
+        <v>120.0292691405698</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -4885,7 +4885,7 @@
     </row>
     <row r="7" spans="1:20">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -4924,22 +4924,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.6352497018953425</v>
+        <v>0.6352497018953469</v>
       </c>
       <c r="O7">
         <v>1.100000023837896</v>
       </c>
       <c r="P7">
-        <v>0.6353189520057179</v>
+        <v>0.6353189520057145</v>
       </c>
       <c r="Q7">
-        <v>59.96712042494714</v>
+        <v>59.96712042494728</v>
       </c>
       <c r="R7">
         <v>-89.99999999999636</v>
       </c>
       <c r="S7">
-        <v>120.0292691517804</v>
+        <v>120.0292691517807</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -4947,7 +4947,7 @@
     </row>
     <row r="8" spans="1:20">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -4986,22 +4986,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.6352497018953425</v>
+        <v>0.6352497018953469</v>
       </c>
       <c r="O8">
         <v>1.100000023837896</v>
       </c>
       <c r="P8">
-        <v>0.6353189520057179</v>
+        <v>0.6353189520057144</v>
       </c>
       <c r="Q8">
-        <v>59.96712042494714</v>
+        <v>59.96712042494728</v>
       </c>
       <c r="R8">
         <v>-89.99999999999636</v>
       </c>
       <c r="S8">
-        <v>120.0292691517804</v>
+        <v>120.0292691517806</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -5009,7 +5009,7 @@
     </row>
     <row r="9" spans="1:20">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -5048,22 +5048,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.6352497018953425</v>
+        <v>0.6352497018953468</v>
       </c>
       <c r="O9">
         <v>1.100000023837896</v>
       </c>
       <c r="P9">
-        <v>0.6353189520057178</v>
+        <v>0.6353189520057145</v>
       </c>
       <c r="Q9">
-        <v>59.96712042494715</v>
+        <v>59.96712042494729</v>
       </c>
       <c r="R9">
         <v>-89.99999999999636</v>
       </c>
       <c r="S9">
-        <v>120.0292691517804</v>
+        <v>120.0292691517806</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -5143,10 +5143,10 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B2">
-        <v>2.884943122233677</v>
+        <v>2.884943122233687</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -5155,7 +5155,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>33.31245376436745</v>
+        <v>33.31245376436758</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -5164,48 +5164,48 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0.4394678541080544</v>
+        <v>0.4394678541080853</v>
       </c>
       <c r="I2">
-        <v>4.386313816163039</v>
+        <v>4.386313816163026</v>
       </c>
       <c r="J2">
-        <v>0.437816359011731</v>
+        <v>0.4378163590117598</v>
       </c>
       <c r="K2">
-        <v>4.378163482065634</v>
+        <v>4.378163482065609</v>
       </c>
       <c r="L2">
-        <v>0.4378163589897447</v>
+        <v>0.4378163589897711</v>
       </c>
       <c r="M2">
-        <v>4.378163482065386</v>
+        <v>4.378163482065364</v>
       </c>
       <c r="N2">
-        <v>0.6352497015657841</v>
+        <v>0.6352497015657778</v>
       </c>
       <c r="O2">
-        <v>1.100000023837896</v>
+        <v>1.100000023837897</v>
       </c>
       <c r="P2">
-        <v>0.6353189522056994</v>
+        <v>0.6353189522057014</v>
       </c>
       <c r="Q2">
-        <v>59.96712042125095</v>
+        <v>59.9671204212512</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999635</v>
+        <v>-89.99999999999636</v>
       </c>
       <c r="S2">
-        <v>120.0292691278696</v>
+        <v>120.0292691278689</v>
       </c>
       <c r="T2">
-        <v>2.884943122233677</v>
+        <v>2.884943122233687</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -5244,22 +5244,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.635249701659989</v>
+        <v>0.6352497016599825</v>
       </c>
       <c r="O3">
-        <v>1.100000023837896</v>
+        <v>1.100000023837897</v>
       </c>
       <c r="P3">
-        <v>0.6353189521750797</v>
+        <v>0.6353189521750811</v>
       </c>
       <c r="Q3">
-        <v>59.96712041954462</v>
+        <v>59.96712041954493</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999635</v>
+        <v>-89.99999999999638</v>
       </c>
       <c r="S3">
-        <v>120.0292691360832</v>
+        <v>120.0292691360825</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -5267,7 +5267,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -5306,22 +5306,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.6352497017014846</v>
+        <v>0.6352497017014783</v>
       </c>
       <c r="O4">
-        <v>1.100000023837896</v>
+        <v>1.100000023837897</v>
       </c>
       <c r="P4">
-        <v>0.6353189521783057</v>
+        <v>0.635318952178307</v>
       </c>
       <c r="Q4">
-        <v>59.96712041705343</v>
+        <v>59.96712041705373</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999635</v>
+        <v>-89.99999999999638</v>
       </c>
       <c r="S4">
-        <v>120.0292691405693</v>
+        <v>120.0292691405685</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -5329,7 +5329,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -5368,22 +5368,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.6352497017014846</v>
+        <v>0.6352497017014782</v>
       </c>
       <c r="O5">
-        <v>1.100000023837896</v>
+        <v>1.100000023837897</v>
       </c>
       <c r="P5">
-        <v>0.6353189521783058</v>
+        <v>0.6353189521783069</v>
       </c>
       <c r="Q5">
-        <v>59.96712041705342</v>
+        <v>59.96712041705375</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999635</v>
+        <v>-89.99999999999638</v>
       </c>
       <c r="S5">
-        <v>120.0292691405693</v>
+        <v>120.0292691405685</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -5391,7 +5391,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -5430,22 +5430,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.6352497017014845</v>
+        <v>0.6352497017014783</v>
       </c>
       <c r="O6">
-        <v>1.100000023837896</v>
+        <v>1.100000023837897</v>
       </c>
       <c r="P6">
-        <v>0.6353189521783057</v>
+        <v>0.635318952178307</v>
       </c>
       <c r="Q6">
-        <v>59.96712041705343</v>
+        <v>59.96712041705373</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999635</v>
+        <v>-89.99999999999638</v>
       </c>
       <c r="S6">
-        <v>120.0292691405693</v>
+        <v>120.0292691405685</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -5453,7 +5453,7 @@
     </row>
     <row r="7" spans="1:20">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -5492,22 +5492,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.6352497019045694</v>
+        <v>0.635249701904563</v>
       </c>
       <c r="O7">
-        <v>1.100000023837896</v>
+        <v>1.100000023837897</v>
       </c>
       <c r="P7">
-        <v>0.6353189519975032</v>
+        <v>0.6353189519975045</v>
       </c>
       <c r="Q7">
-        <v>59.96712042532285</v>
+        <v>59.96712042532315</v>
       </c>
       <c r="R7">
-        <v>-89.99999999999635</v>
+        <v>-89.99999999999638</v>
       </c>
       <c r="S7">
-        <v>120.029269152314</v>
+        <v>120.0292691523133</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -5515,7 +5515,7 @@
     </row>
     <row r="8" spans="1:20">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -5554,22 +5554,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.6352497019045693</v>
+        <v>0.6352497019045629</v>
       </c>
       <c r="O8">
-        <v>1.100000023837896</v>
+        <v>1.100000023837897</v>
       </c>
       <c r="P8">
-        <v>0.6353189519975031</v>
+        <v>0.6353189519975044</v>
       </c>
       <c r="Q8">
-        <v>59.96712042532286</v>
+        <v>59.96712042532318</v>
       </c>
       <c r="R8">
-        <v>-89.99999999999635</v>
+        <v>-89.99999999999638</v>
       </c>
       <c r="S8">
-        <v>120.029269152314</v>
+        <v>120.0292691523132</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -5577,7 +5577,7 @@
     </row>
     <row r="9" spans="1:20">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -5616,22 +5616,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.6352497019045693</v>
+        <v>0.635249701904563</v>
       </c>
       <c r="O9">
-        <v>1.100000023837896</v>
+        <v>1.100000023837897</v>
       </c>
       <c r="P9">
-        <v>0.6353189519975031</v>
+        <v>0.6353189519975045</v>
       </c>
       <c r="Q9">
-        <v>59.96712042532286</v>
+        <v>59.96712042532315</v>
       </c>
       <c r="R9">
-        <v>-89.99999999999635</v>
+        <v>-89.99999999999638</v>
       </c>
       <c r="S9">
-        <v>120.029269152314</v>
+        <v>120.0292691523133</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -5711,7 +5711,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>1.171389535180247</v>
@@ -5732,37 +5732,37 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0.4394678541080387</v>
+        <v>0.4394678541080334</v>
       </c>
       <c r="I2">
-        <v>4.386313816163039</v>
+        <v>4.386313816163042</v>
       </c>
       <c r="J2">
-        <v>0.4378163590117159</v>
+        <v>0.4378163590117204</v>
       </c>
       <c r="K2">
-        <v>4.378163482065635</v>
+        <v>4.378163482065638</v>
       </c>
       <c r="L2">
-        <v>0.4378163589897304</v>
+        <v>0.437816358989736</v>
       </c>
       <c r="M2">
-        <v>4.378163482065387</v>
+        <v>4.378163482065375</v>
       </c>
       <c r="N2">
-        <v>0.8439038960710538</v>
+        <v>0.8439038960710545</v>
       </c>
       <c r="O2">
         <v>1.100000023840151</v>
       </c>
       <c r="P2">
-        <v>0.972783586032295</v>
+        <v>0.9727835860322939</v>
       </c>
       <c r="Q2">
-        <v>31.71020211139843</v>
+        <v>31.71020211139852</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999653</v>
+        <v>-89.99999999999655</v>
       </c>
       <c r="S2">
         <v>137.5621575052569</v>
@@ -5773,7 +5773,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -5812,22 +5812,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8439038961003684</v>
+        <v>0.8439038961003696</v>
       </c>
       <c r="O3">
         <v>1.100000023840151</v>
       </c>
       <c r="P3">
-        <v>0.9727835860155372</v>
+        <v>0.9727835860155361</v>
       </c>
       <c r="Q3">
-        <v>31.7102021131463</v>
+        <v>31.71020211314639</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999653</v>
+        <v>-89.99999999999655</v>
       </c>
       <c r="S3">
-        <v>137.562157507332</v>
+        <v>137.5621575073321</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -5835,7 +5835,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -5874,22 +5874,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8439038961195058</v>
+        <v>0.8439038961195072</v>
       </c>
       <c r="O4">
         <v>1.100000023840151</v>
       </c>
       <c r="P4">
-        <v>0.972783586014427</v>
+        <v>0.972783586014426</v>
       </c>
       <c r="Q4">
-        <v>31.7102021135936</v>
+        <v>31.71020211359368</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999653</v>
+        <v>-89.99999999999655</v>
       </c>
       <c r="S4">
-        <v>137.5621575085223</v>
+        <v>137.5621575085224</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -5897,7 +5897,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -5936,22 +5936,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8439038961195058</v>
+        <v>0.8439038961195072</v>
       </c>
       <c r="O5">
         <v>1.100000023840151</v>
       </c>
       <c r="P5">
-        <v>0.972783586014427</v>
+        <v>0.9727835860144258</v>
       </c>
       <c r="Q5">
-        <v>31.7102021135936</v>
+        <v>31.71020211359369</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999653</v>
+        <v>-89.99999999999655</v>
       </c>
       <c r="S5">
-        <v>137.5621575085223</v>
+        <v>137.5621575085224</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -5959,7 +5959,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -5998,22 +5998,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.843903896119506</v>
+        <v>0.8439038961195072</v>
       </c>
       <c r="O6">
         <v>1.100000023840151</v>
       </c>
       <c r="P6">
-        <v>0.972783586014427</v>
+        <v>0.972783586014426</v>
       </c>
       <c r="Q6">
-        <v>31.7102021135936</v>
+        <v>31.71020211359369</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999653</v>
+        <v>-89.99999999999655</v>
       </c>
       <c r="S6">
-        <v>137.5621575085223</v>
+        <v>137.5621575085224</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -6021,7 +6021,7 @@
     </row>
     <row r="7" spans="1:20">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -6060,22 +6060,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.8439038961390181</v>
+        <v>0.8439038961390193</v>
       </c>
       <c r="O7">
         <v>1.100000023840151</v>
       </c>
       <c r="P7">
-        <v>0.9727835859388282</v>
+        <v>0.9727835859388271</v>
       </c>
       <c r="Q7">
-        <v>31.71020211930536</v>
+        <v>31.71020211930545</v>
       </c>
       <c r="R7">
-        <v>-89.99999999999653</v>
+        <v>-89.99999999999655</v>
       </c>
       <c r="S7">
-        <v>137.5621575109813</v>
+        <v>137.5621575109814</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -6083,7 +6083,7 @@
     </row>
     <row r="8" spans="1:20">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -6122,22 +6122,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.8439038961390178</v>
+        <v>0.8439038961390193</v>
       </c>
       <c r="O8">
         <v>1.100000023840151</v>
       </c>
       <c r="P8">
-        <v>0.9727835859388282</v>
+        <v>0.9727835859388271</v>
       </c>
       <c r="Q8">
-        <v>31.71020211930536</v>
+        <v>31.71020211930545</v>
       </c>
       <c r="R8">
-        <v>-89.99999999999653</v>
+        <v>-89.99999999999655</v>
       </c>
       <c r="S8">
-        <v>137.5621575109813</v>
+        <v>137.5621575109814</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -6145,7 +6145,7 @@
     </row>
     <row r="9" spans="1:20">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -6184,22 +6184,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.8439038961390178</v>
+        <v>0.8439038961390193</v>
       </c>
       <c r="O9">
         <v>1.100000023840151</v>
       </c>
       <c r="P9">
-        <v>0.9727835859388282</v>
+        <v>0.9727835859388271</v>
       </c>
       <c r="Q9">
-        <v>31.71020211930536</v>
+        <v>31.71020211930545</v>
       </c>
       <c r="R9">
-        <v>-89.99999999999653</v>
+        <v>-89.99999999999655</v>
       </c>
       <c r="S9">
-        <v>137.5621575109813</v>
+        <v>137.5621575109814</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -6240,7 +6240,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>2.886751509919007</v>
@@ -6263,7 +6263,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -6286,7 +6286,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -6309,7 +6309,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -6332,7 +6332,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -6355,7 +6355,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -6378,7 +6378,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -6401,7 +6401,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -6496,7 +6496,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>1.171389535180246</v>
@@ -6508,7 +6508,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>13.52604126924451</v>
+        <v>13.52604126924452</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -6517,40 +6517,40 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0.4394678541080544</v>
+        <v>0.4394678541080853</v>
       </c>
       <c r="I2">
-        <v>4.386313816163039</v>
+        <v>4.386313816163026</v>
       </c>
       <c r="J2">
-        <v>0.437816359011731</v>
+        <v>0.4378163590117598</v>
       </c>
       <c r="K2">
-        <v>4.378163482065634</v>
+        <v>4.378163482065609</v>
       </c>
       <c r="L2">
-        <v>0.4378163589897447</v>
+        <v>0.4378163589897711</v>
       </c>
       <c r="M2">
-        <v>4.378163482065386</v>
+        <v>4.378163482065364</v>
       </c>
       <c r="N2">
-        <v>0.843903896071053</v>
+        <v>0.8439038960710515</v>
       </c>
       <c r="O2">
         <v>1.100000023840151</v>
       </c>
       <c r="P2">
-        <v>0.9727835860322953</v>
+        <v>0.9727835860322944</v>
       </c>
       <c r="Q2">
-        <v>31.71020211139839</v>
+        <v>31.71020211139844</v>
       </c>
       <c r="R2">
         <v>-89.99999999999655</v>
       </c>
       <c r="S2">
-        <v>137.5621575052568</v>
+        <v>137.5621575052567</v>
       </c>
       <c r="T2">
         <v>1.171389535180246</v>
@@ -6558,7 +6558,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -6597,22 +6597,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8439038961003676</v>
+        <v>0.843903896100366</v>
       </c>
       <c r="O3">
         <v>1.100000023840151</v>
       </c>
       <c r="P3">
-        <v>0.9727835860155376</v>
+        <v>0.9727835860155363</v>
       </c>
       <c r="Q3">
-        <v>31.71020211314625</v>
+        <v>31.71020211314633</v>
       </c>
       <c r="R3">
         <v>-89.99999999999655</v>
       </c>
       <c r="S3">
-        <v>137.5621575073319</v>
+        <v>137.5621575073318</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -6620,7 +6620,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -6659,16 +6659,16 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8439038961195052</v>
+        <v>0.8439038961195036</v>
       </c>
       <c r="O4">
         <v>1.100000023840151</v>
       </c>
       <c r="P4">
-        <v>0.9727835860144274</v>
+        <v>0.972783586014426</v>
       </c>
       <c r="Q4">
-        <v>31.71020211359355</v>
+        <v>31.71020211359363</v>
       </c>
       <c r="R4">
         <v>-89.99999999999655</v>
@@ -6682,7 +6682,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -6721,22 +6721,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8439038961195052</v>
+        <v>0.8439038961195036</v>
       </c>
       <c r="O5">
         <v>1.100000023840151</v>
       </c>
       <c r="P5">
-        <v>0.9727835860144274</v>
+        <v>0.972783586014426</v>
       </c>
       <c r="Q5">
-        <v>31.71020211359355</v>
+        <v>31.71020211359364</v>
       </c>
       <c r="R5">
         <v>-89.99999999999655</v>
       </c>
       <c r="S5">
-        <v>137.5621575085222</v>
+        <v>137.5621575085221</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -6744,7 +6744,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -6783,22 +6783,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.8439038961195052</v>
+        <v>0.8439038961195036</v>
       </c>
       <c r="O6">
         <v>1.100000023840151</v>
       </c>
       <c r="P6">
-        <v>0.9727835860144274</v>
+        <v>0.972783586014426</v>
       </c>
       <c r="Q6">
-        <v>31.71020211359355</v>
+        <v>31.71020211359363</v>
       </c>
       <c r="R6">
         <v>-89.99999999999655</v>
       </c>
       <c r="S6">
-        <v>137.5621575085222</v>
+        <v>137.5621575085221</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -6806,7 +6806,7 @@
     </row>
     <row r="7" spans="1:20">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -6845,16 +6845,16 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.8439038961399463</v>
+        <v>0.8439038961399449</v>
       </c>
       <c r="O7">
         <v>1.100000023840151</v>
       </c>
       <c r="P7">
-        <v>0.9727835859352285</v>
+        <v>0.9727835859352274</v>
       </c>
       <c r="Q7">
-        <v>31.71020211957731</v>
+        <v>31.71020211957738</v>
       </c>
       <c r="R7">
         <v>-89.99999999999655</v>
@@ -6868,7 +6868,7 @@
     </row>
     <row r="8" spans="1:20">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -6907,16 +6907,16 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.8439038961399463</v>
+        <v>0.8439038961399447</v>
       </c>
       <c r="O8">
         <v>1.100000023840151</v>
       </c>
       <c r="P8">
-        <v>0.9727835859352285</v>
+        <v>0.9727835859352271</v>
       </c>
       <c r="Q8">
-        <v>31.71020211957731</v>
+        <v>31.71020211957739</v>
       </c>
       <c r="R8">
         <v>-89.99999999999655</v>
@@ -6930,7 +6930,7 @@
     </row>
     <row r="9" spans="1:20">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -6969,16 +6969,16 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.8439038961399463</v>
+        <v>0.8439038961399447</v>
       </c>
       <c r="O9">
         <v>1.100000023840151</v>
       </c>
       <c r="P9">
-        <v>0.9727835859352285</v>
+        <v>0.9727835859352271</v>
       </c>
       <c r="Q9">
-        <v>31.71020211957731</v>
+        <v>31.71020211957738</v>
       </c>
       <c r="R9">
         <v>-89.99999999999655</v>
@@ -7064,10 +7064,10 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B2">
-        <v>2.307756953396991</v>
+        <v>2.307756953397001</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -7076,7 +7076,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>26.64768196535967</v>
+        <v>26.64768196535978</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -7085,48 +7085,48 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0.4996558650496629</v>
+        <v>0.4996558650497021</v>
       </c>
       <c r="I2">
-        <v>4.985712340297961</v>
+        <v>4.985712340297939</v>
       </c>
       <c r="J2">
-        <v>0.497518590387613</v>
+        <v>0.4975185903876545</v>
       </c>
       <c r="K2">
-        <v>4.975185774943886</v>
+        <v>4.975185774943863</v>
       </c>
       <c r="L2">
-        <v>0.497518590407994</v>
+        <v>0.4975185904080356</v>
       </c>
       <c r="M2">
-        <v>4.975185774943612</v>
+        <v>4.975185774943586</v>
       </c>
       <c r="N2">
-        <v>0.5775199950542024</v>
+        <v>0.5775199950541998</v>
       </c>
       <c r="O2">
-        <v>0.999999999996292</v>
+        <v>0.9999999999962927</v>
       </c>
       <c r="P2">
-        <v>0.5775918160830034</v>
+        <v>0.5775918160830037</v>
       </c>
       <c r="Q2">
-        <v>59.96262536179988</v>
+        <v>59.96262536180005</v>
       </c>
       <c r="R2">
         <v>-89.99999999999635</v>
       </c>
       <c r="S2">
-        <v>120.0332552040494</v>
+        <v>120.033255204049</v>
       </c>
       <c r="T2">
-        <v>2.307756953396991</v>
+        <v>2.307756953397001</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -7165,22 +7165,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.577519995166437</v>
+        <v>0.5775199951664352</v>
       </c>
       <c r="O3">
-        <v>0.9999999999962922</v>
+        <v>0.9999999999962927</v>
       </c>
       <c r="P3">
-        <v>0.5775918160817635</v>
+        <v>0.5775918160817638</v>
       </c>
       <c r="Q3">
-        <v>59.96262535553143</v>
+        <v>59.96262535553157</v>
       </c>
       <c r="R3">
         <v>-89.99999999999635</v>
       </c>
       <c r="S3">
-        <v>120.0332552168252</v>
+        <v>120.0332552168249</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -7188,7 +7188,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -7227,22 +7227,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.5775199952228665</v>
+        <v>0.5775199952228647</v>
       </c>
       <c r="O4">
-        <v>0.999999999996292</v>
+        <v>0.999999999996293</v>
       </c>
       <c r="P4">
-        <v>0.5775918161033989</v>
+        <v>0.577591816103399</v>
       </c>
       <c r="Q4">
-        <v>59.96262534983165</v>
+        <v>59.96262534983181</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999635</v>
+        <v>-89.99999999999636</v>
       </c>
       <c r="S4">
-        <v>120.0332552245198</v>
+        <v>120.0332552245195</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -7250,7 +7250,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -7289,22 +7289,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.5775199952228666</v>
+        <v>0.5775199952228647</v>
       </c>
       <c r="O5">
-        <v>0.9999999999962922</v>
+        <v>0.9999999999962927</v>
       </c>
       <c r="P5">
         <v>0.577591816103399</v>
       </c>
       <c r="Q5">
-        <v>59.96262534983163</v>
+        <v>59.96262534983181</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999635</v>
+        <v>-89.99999999999636</v>
       </c>
       <c r="S5">
-        <v>120.0332552245198</v>
+        <v>120.0332552245195</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -7312,7 +7312,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -7351,22 +7351,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.5775199952228665</v>
+        <v>0.5775199952228646</v>
       </c>
       <c r="O6">
-        <v>0.9999999999962922</v>
+        <v>0.9999999999962927</v>
       </c>
       <c r="P6">
-        <v>0.5775918161033989</v>
+        <v>0.5775918161033992</v>
       </c>
       <c r="Q6">
-        <v>59.96262534983166</v>
+        <v>59.96262534983181</v>
       </c>
       <c r="R6">
         <v>-89.99999999999635</v>
       </c>
       <c r="S6">
-        <v>120.0332552245198</v>
+        <v>120.0332552245195</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -7374,7 +7374,7 @@
     </row>
     <row r="7" spans="1:20">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -7413,22 +7413,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.5775199954079533</v>
+        <v>0.5775199954079513</v>
       </c>
       <c r="O7">
-        <v>0.999999999996292</v>
+        <v>0.9999999999962927</v>
       </c>
       <c r="P7">
-        <v>0.5775918159386202</v>
+        <v>0.5775918159386204</v>
       </c>
       <c r="Q7">
-        <v>59.96262535812352</v>
+        <v>59.96262535812367</v>
       </c>
       <c r="R7">
-        <v>-89.99999999999635</v>
+        <v>-89.99999999999636</v>
       </c>
       <c r="S7">
-        <v>120.0332552362949</v>
+        <v>120.0332552362946</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -7436,7 +7436,7 @@
     </row>
     <row r="8" spans="1:20">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -7475,22 +7475,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.5775199954079534</v>
+        <v>0.5775199954079515</v>
       </c>
       <c r="O8">
-        <v>0.999999999996292</v>
+        <v>0.9999999999962927</v>
       </c>
       <c r="P8">
-        <v>0.5775918159386204</v>
+        <v>0.5775918159386205</v>
       </c>
       <c r="Q8">
-        <v>59.9626253581235</v>
+        <v>59.96262535812366</v>
       </c>
       <c r="R8">
-        <v>-89.99999999999635</v>
+        <v>-89.99999999999636</v>
       </c>
       <c r="S8">
-        <v>120.0332552362949</v>
+        <v>120.0332552362946</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -7498,7 +7498,7 @@
     </row>
     <row r="9" spans="1:20">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -7537,22 +7537,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.5775199954079532</v>
+        <v>0.5775199954079513</v>
       </c>
       <c r="O9">
-        <v>0.999999999996292</v>
+        <v>0.9999999999962927</v>
       </c>
       <c r="P9">
-        <v>0.5775918159386202</v>
+        <v>0.5775918159386205</v>
       </c>
       <c r="Q9">
-        <v>59.96262535812353</v>
+        <v>59.96262535812367</v>
       </c>
       <c r="R9">
         <v>-89.99999999999635</v>
       </c>
       <c r="S9">
-        <v>120.0332552362949</v>
+        <v>120.0332552362946</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -7632,10 +7632,10 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B2">
-        <v>2.307756953396991</v>
+        <v>2.307756953397001</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -7644,7 +7644,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>26.64768196535967</v>
+        <v>26.64768196535978</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -7653,48 +7653,48 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0.4996558650496629</v>
+        <v>0.4996558650497021</v>
       </c>
       <c r="I2">
-        <v>4.985712340297961</v>
+        <v>4.985712340297939</v>
       </c>
       <c r="J2">
-        <v>0.497518590387613</v>
+        <v>0.4975185903876545</v>
       </c>
       <c r="K2">
-        <v>4.975185774943886</v>
+        <v>4.975185774943863</v>
       </c>
       <c r="L2">
-        <v>0.497518590407994</v>
+        <v>0.4975185904080356</v>
       </c>
       <c r="M2">
-        <v>4.975185774943612</v>
+        <v>4.975185774943586</v>
       </c>
       <c r="N2">
-        <v>0.5775199950542024</v>
+        <v>0.5775199950541998</v>
       </c>
       <c r="O2">
-        <v>0.999999999996292</v>
+        <v>0.9999999999962927</v>
       </c>
       <c r="P2">
-        <v>0.5775918160830034</v>
+        <v>0.5775918160830037</v>
       </c>
       <c r="Q2">
-        <v>59.96262536179988</v>
+        <v>59.96262536180005</v>
       </c>
       <c r="R2">
         <v>-89.99999999999635</v>
       </c>
       <c r="S2">
-        <v>120.0332552040494</v>
+        <v>120.033255204049</v>
       </c>
       <c r="T2">
-        <v>2.307756953396991</v>
+        <v>2.307756953397001</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -7733,22 +7733,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.577519995166437</v>
+        <v>0.5775199951664352</v>
       </c>
       <c r="O3">
-        <v>0.9999999999962922</v>
+        <v>0.9999999999962927</v>
       </c>
       <c r="P3">
-        <v>0.5775918160817635</v>
+        <v>0.5775918160817638</v>
       </c>
       <c r="Q3">
-        <v>59.96262535553143</v>
+        <v>59.96262535553157</v>
       </c>
       <c r="R3">
         <v>-89.99999999999635</v>
       </c>
       <c r="S3">
-        <v>120.0332552168252</v>
+        <v>120.0332552168249</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -7756,7 +7756,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -7795,22 +7795,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.5775199952228665</v>
+        <v>0.5775199952228647</v>
       </c>
       <c r="O4">
-        <v>0.999999999996292</v>
+        <v>0.999999999996293</v>
       </c>
       <c r="P4">
-        <v>0.5775918161033989</v>
+        <v>0.577591816103399</v>
       </c>
       <c r="Q4">
-        <v>59.96262534983165</v>
+        <v>59.96262534983181</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999635</v>
+        <v>-89.99999999999636</v>
       </c>
       <c r="S4">
-        <v>120.0332552245198</v>
+        <v>120.0332552245195</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -7818,7 +7818,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -7857,22 +7857,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.5775199952228666</v>
+        <v>0.5775199952228647</v>
       </c>
       <c r="O5">
-        <v>0.9999999999962922</v>
+        <v>0.9999999999962927</v>
       </c>
       <c r="P5">
         <v>0.577591816103399</v>
       </c>
       <c r="Q5">
-        <v>59.96262534983163</v>
+        <v>59.96262534983181</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999635</v>
+        <v>-89.99999999999636</v>
       </c>
       <c r="S5">
-        <v>120.0332552245198</v>
+        <v>120.0332552245195</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -7880,7 +7880,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -7919,22 +7919,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.5775199952228665</v>
+        <v>0.5775199952228646</v>
       </c>
       <c r="O6">
-        <v>0.9999999999962922</v>
+        <v>0.9999999999962927</v>
       </c>
       <c r="P6">
-        <v>0.5775918161033989</v>
+        <v>0.5775918161033992</v>
       </c>
       <c r="Q6">
-        <v>59.96262534983166</v>
+        <v>59.96262534983181</v>
       </c>
       <c r="R6">
         <v>-89.99999999999635</v>
       </c>
       <c r="S6">
-        <v>120.0332552245198</v>
+        <v>120.0332552245195</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -7942,7 +7942,7 @@
     </row>
     <row r="7" spans="1:20">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -7981,22 +7981,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.5775199954079533</v>
+        <v>0.5775199954079513</v>
       </c>
       <c r="O7">
-        <v>0.999999999996292</v>
+        <v>0.9999999999962927</v>
       </c>
       <c r="P7">
-        <v>0.5775918159386202</v>
+        <v>0.5775918159386204</v>
       </c>
       <c r="Q7">
-        <v>59.96262535812352</v>
+        <v>59.96262535812367</v>
       </c>
       <c r="R7">
-        <v>-89.99999999999635</v>
+        <v>-89.99999999999636</v>
       </c>
       <c r="S7">
-        <v>120.0332552362949</v>
+        <v>120.0332552362946</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -8004,7 +8004,7 @@
     </row>
     <row r="8" spans="1:20">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -8043,22 +8043,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.5775199954079534</v>
+        <v>0.5775199954079515</v>
       </c>
       <c r="O8">
-        <v>0.999999999996292</v>
+        <v>0.9999999999962927</v>
       </c>
       <c r="P8">
-        <v>0.5775918159386204</v>
+        <v>0.5775918159386205</v>
       </c>
       <c r="Q8">
-        <v>59.9626253581235</v>
+        <v>59.96262535812366</v>
       </c>
       <c r="R8">
-        <v>-89.99999999999635</v>
+        <v>-89.99999999999636</v>
       </c>
       <c r="S8">
-        <v>120.0332552362949</v>
+        <v>120.0332552362946</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -8066,7 +8066,7 @@
     </row>
     <row r="9" spans="1:20">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -8105,22 +8105,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.5775199954079532</v>
+        <v>0.5775199954079513</v>
       </c>
       <c r="O9">
-        <v>0.999999999996292</v>
+        <v>0.9999999999962927</v>
       </c>
       <c r="P9">
-        <v>0.5775918159386202</v>
+        <v>0.5775918159386205</v>
       </c>
       <c r="Q9">
-        <v>59.96262535812353</v>
+        <v>59.96262535812367</v>
       </c>
       <c r="R9">
         <v>-89.99999999999635</v>
       </c>
       <c r="S9">
-        <v>120.0332552362949</v>
+        <v>120.0332552362946</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -8200,7 +8200,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>1.013500203418938</v>
@@ -8221,37 +8221,37 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0.4996558650496629</v>
+        <v>0.4996558650497021</v>
       </c>
       <c r="I2">
-        <v>4.985712340297961</v>
+        <v>4.985712340297939</v>
       </c>
       <c r="J2">
-        <v>0.497518590387613</v>
+        <v>0.4975185903876545</v>
       </c>
       <c r="K2">
-        <v>4.975185774943886</v>
+        <v>4.975185774943863</v>
       </c>
       <c r="L2">
-        <v>0.497518590407994</v>
+        <v>0.4975185904080356</v>
       </c>
       <c r="M2">
-        <v>4.975185774943612</v>
+        <v>4.975185774943586</v>
       </c>
       <c r="N2">
-        <v>0.7490476618058506</v>
+        <v>0.7490476618058505</v>
       </c>
       <c r="O2">
-        <v>0.9999999999988021</v>
+        <v>0.9999999999988024</v>
       </c>
       <c r="P2">
-        <v>0.8719217209770547</v>
+        <v>0.8719217209770538</v>
       </c>
       <c r="Q2">
-        <v>32.31421581781562</v>
+        <v>32.31421581781571</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999653</v>
+        <v>-89.99999999999655</v>
       </c>
       <c r="S2">
         <v>136.5546704245691</v>
@@ -8262,7 +8262,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -8301,16 +8301,16 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.749047661858511</v>
+        <v>0.7490476618585112</v>
       </c>
       <c r="O3">
-        <v>0.9999999999988021</v>
+        <v>0.9999999999988024</v>
       </c>
       <c r="P3">
-        <v>0.8719217209699948</v>
+        <v>0.8719217209699934</v>
       </c>
       <c r="Q3">
-        <v>32.31421581939507</v>
+        <v>32.31421581939517</v>
       </c>
       <c r="R3">
         <v>-89.99999999999655</v>
@@ -8324,7 +8324,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -8363,22 +8363,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.7490476618937274</v>
+        <v>0.7490476618937276</v>
       </c>
       <c r="O4">
-        <v>0.9999999999988021</v>
+        <v>0.9999999999988024</v>
       </c>
       <c r="P4">
-        <v>0.8719217209755066</v>
+        <v>0.8719217209755051</v>
       </c>
       <c r="Q4">
-        <v>32.31421581964373</v>
+        <v>32.31421581964384</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999653</v>
+        <v>-89.99999999999655</v>
       </c>
       <c r="S4">
-        <v>136.5546704305525</v>
+        <v>136.5546704305526</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -8386,7 +8386,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -8425,22 +8425,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.7490476618937274</v>
+        <v>0.7490476618937277</v>
       </c>
       <c r="O5">
-        <v>0.9999999999988021</v>
+        <v>0.9999999999988024</v>
       </c>
       <c r="P5">
-        <v>0.8719217209755066</v>
+        <v>0.8719217209755055</v>
       </c>
       <c r="Q5">
-        <v>32.31421581964373</v>
+        <v>32.31421581964383</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999653</v>
+        <v>-89.99999999999655</v>
       </c>
       <c r="S5">
-        <v>136.5546704305525</v>
+        <v>136.5546704305526</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -8448,7 +8448,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -8487,22 +8487,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.7490476618937274</v>
+        <v>0.7490476618937276</v>
       </c>
       <c r="O6">
-        <v>0.9999999999988021</v>
+        <v>0.9999999999988024</v>
       </c>
       <c r="P6">
-        <v>0.8719217209755066</v>
+        <v>0.8719217209755055</v>
       </c>
       <c r="Q6">
-        <v>32.31421581964373</v>
+        <v>32.31421581964384</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999653</v>
+        <v>-89.99999999999655</v>
       </c>
       <c r="S6">
-        <v>136.5546704305525</v>
+        <v>136.5546704305526</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -8510,7 +8510,7 @@
     </row>
     <row r="7" spans="1:20">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -8549,19 +8549,19 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.7490476619166747</v>
+        <v>0.749047661916675</v>
       </c>
       <c r="O7">
-        <v>0.9999999999988021</v>
+        <v>0.9999999999988024</v>
       </c>
       <c r="P7">
-        <v>0.8719217208976143</v>
+        <v>0.8719217208976131</v>
       </c>
       <c r="Q7">
-        <v>32.31421582623618</v>
+        <v>32.31421582623629</v>
       </c>
       <c r="R7">
-        <v>-89.99999999999653</v>
+        <v>-89.99999999999655</v>
       </c>
       <c r="S7">
         <v>136.5546704334073</v>
@@ -8572,7 +8572,7 @@
     </row>
     <row r="8" spans="1:20">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -8611,19 +8611,19 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.7490476619166747</v>
+        <v>0.7490476619166749</v>
       </c>
       <c r="O8">
-        <v>0.9999999999988021</v>
+        <v>0.9999999999988024</v>
       </c>
       <c r="P8">
-        <v>0.8719217208976144</v>
+        <v>0.8719217208976131</v>
       </c>
       <c r="Q8">
-        <v>32.31421582623618</v>
+        <v>32.31421582623629</v>
       </c>
       <c r="R8">
-        <v>-89.99999999999653</v>
+        <v>-89.99999999999655</v>
       </c>
       <c r="S8">
         <v>136.5546704334073</v>
@@ -8634,7 +8634,7 @@
     </row>
     <row r="9" spans="1:20">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -8673,19 +8673,19 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.7490476619166747</v>
+        <v>0.7490476619166749</v>
       </c>
       <c r="O9">
-        <v>0.9999999999988021</v>
+        <v>0.9999999999988024</v>
       </c>
       <c r="P9">
-        <v>0.8719217208976143</v>
+        <v>0.8719217208976131</v>
       </c>
       <c r="Q9">
-        <v>32.31421582623618</v>
+        <v>32.31421582623629</v>
       </c>
       <c r="R9">
-        <v>-89.99999999999653</v>
+        <v>-89.99999999999655</v>
       </c>
       <c r="S9">
         <v>136.5546704334073</v>
@@ -8768,7 +8768,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>1.013500203418938</v>
@@ -8789,37 +8789,37 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0.4996558650496629</v>
+        <v>0.4996558650497021</v>
       </c>
       <c r="I2">
-        <v>4.985712340297961</v>
+        <v>4.985712340297939</v>
       </c>
       <c r="J2">
-        <v>0.497518590387613</v>
+        <v>0.4975185903876545</v>
       </c>
       <c r="K2">
-        <v>4.975185774943886</v>
+        <v>4.975185774943863</v>
       </c>
       <c r="L2">
-        <v>0.497518590407994</v>
+        <v>0.4975185904080356</v>
       </c>
       <c r="M2">
-        <v>4.975185774943612</v>
+        <v>4.975185774943586</v>
       </c>
       <c r="N2">
-        <v>0.7490476618058506</v>
+        <v>0.7490476618058505</v>
       </c>
       <c r="O2">
-        <v>0.9999999999988021</v>
+        <v>0.9999999999988024</v>
       </c>
       <c r="P2">
-        <v>0.8719217209770547</v>
+        <v>0.8719217209770538</v>
       </c>
       <c r="Q2">
-        <v>32.31421581781562</v>
+        <v>32.31421581781571</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999653</v>
+        <v>-89.99999999999655</v>
       </c>
       <c r="S2">
         <v>136.5546704245691</v>
@@ -8830,7 +8830,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -8869,16 +8869,16 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.749047661858511</v>
+        <v>0.7490476618585112</v>
       </c>
       <c r="O3">
-        <v>0.9999999999988021</v>
+        <v>0.9999999999988024</v>
       </c>
       <c r="P3">
-        <v>0.8719217209699948</v>
+        <v>0.8719217209699934</v>
       </c>
       <c r="Q3">
-        <v>32.31421581939507</v>
+        <v>32.31421581939517</v>
       </c>
       <c r="R3">
         <v>-89.99999999999655</v>
@@ -8892,7 +8892,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -8931,22 +8931,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.7490476618937274</v>
+        <v>0.7490476618937276</v>
       </c>
       <c r="O4">
-        <v>0.9999999999988021</v>
+        <v>0.9999999999988024</v>
       </c>
       <c r="P4">
-        <v>0.8719217209755066</v>
+        <v>0.8719217209755051</v>
       </c>
       <c r="Q4">
-        <v>32.31421581964373</v>
+        <v>32.31421581964384</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999653</v>
+        <v>-89.99999999999655</v>
       </c>
       <c r="S4">
-        <v>136.5546704305525</v>
+        <v>136.5546704305526</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -8954,7 +8954,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -8993,22 +8993,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.7490476618937274</v>
+        <v>0.7490476618937277</v>
       </c>
       <c r="O5">
-        <v>0.9999999999988021</v>
+        <v>0.9999999999988024</v>
       </c>
       <c r="P5">
-        <v>0.8719217209755066</v>
+        <v>0.8719217209755055</v>
       </c>
       <c r="Q5">
-        <v>32.31421581964373</v>
+        <v>32.31421581964383</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999653</v>
+        <v>-89.99999999999655</v>
       </c>
       <c r="S5">
-        <v>136.5546704305525</v>
+        <v>136.5546704305526</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -9016,7 +9016,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -9055,22 +9055,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.7490476618937274</v>
+        <v>0.7490476618937276</v>
       </c>
       <c r="O6">
-        <v>0.9999999999988021</v>
+        <v>0.9999999999988024</v>
       </c>
       <c r="P6">
-        <v>0.8719217209755066</v>
+        <v>0.8719217209755055</v>
       </c>
       <c r="Q6">
-        <v>32.31421581964373</v>
+        <v>32.31421581964384</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999653</v>
+        <v>-89.99999999999655</v>
       </c>
       <c r="S6">
-        <v>136.5546704305525</v>
+        <v>136.5546704305526</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -9078,7 +9078,7 @@
     </row>
     <row r="7" spans="1:20">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -9117,19 +9117,19 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.7490476619166747</v>
+        <v>0.749047661916675</v>
       </c>
       <c r="O7">
-        <v>0.9999999999988021</v>
+        <v>0.9999999999988024</v>
       </c>
       <c r="P7">
-        <v>0.8719217208976143</v>
+        <v>0.8719217208976131</v>
       </c>
       <c r="Q7">
-        <v>32.31421582623618</v>
+        <v>32.31421582623629</v>
       </c>
       <c r="R7">
-        <v>-89.99999999999653</v>
+        <v>-89.99999999999655</v>
       </c>
       <c r="S7">
         <v>136.5546704334073</v>
@@ -9140,7 +9140,7 @@
     </row>
     <row r="8" spans="1:20">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -9179,19 +9179,19 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.7490476619166747</v>
+        <v>0.7490476619166749</v>
       </c>
       <c r="O8">
-        <v>0.9999999999988021</v>
+        <v>0.9999999999988024</v>
       </c>
       <c r="P8">
-        <v>0.8719217208976144</v>
+        <v>0.8719217208976131</v>
       </c>
       <c r="Q8">
-        <v>32.31421582623618</v>
+        <v>32.31421582623629</v>
       </c>
       <c r="R8">
-        <v>-89.99999999999653</v>
+        <v>-89.99999999999655</v>
       </c>
       <c r="S8">
         <v>136.5546704334073</v>
@@ -9202,7 +9202,7 @@
     </row>
     <row r="9" spans="1:20">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -9241,19 +9241,19 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.7490476619166747</v>
+        <v>0.7490476619166749</v>
       </c>
       <c r="O9">
-        <v>0.9999999999988021</v>
+        <v>0.9999999999988024</v>
       </c>
       <c r="P9">
-        <v>0.8719217208976143</v>
+        <v>0.8719217208976131</v>
       </c>
       <c r="Q9">
-        <v>32.31421582623618</v>
+        <v>32.31421582623629</v>
       </c>
       <c r="R9">
-        <v>-89.99999999999653</v>
+        <v>-89.99999999999655</v>
       </c>
       <c r="S9">
         <v>136.5546704334073</v>
@@ -9336,69 +9336,69 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>2.886005588710061</v>
+        <v>2.886005588710052</v>
       </c>
       <c r="D2">
-        <v>2.885691010138482</v>
+        <v>2.885691010138488</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>33.32472207049036</v>
+        <v>33.32472207049026</v>
       </c>
       <c r="G2">
-        <v>33.32108963003071</v>
+        <v>33.32108963003078</v>
       </c>
       <c r="H2">
-        <v>0.4394678541080287</v>
+        <v>0.4394678541080367</v>
       </c>
       <c r="I2">
-        <v>4.386313816163398</v>
+        <v>4.386313816163413</v>
       </c>
       <c r="J2">
-        <v>0.4378163590167708</v>
+        <v>0.4378163590167795</v>
       </c>
       <c r="K2">
-        <v>4.378163482112574</v>
+        <v>4.378163482112584</v>
       </c>
       <c r="L2">
-        <v>0.4378163589897015</v>
+        <v>0.4378163589897109</v>
       </c>
       <c r="M2">
-        <v>4.378163482065465</v>
+        <v>4.378163482065473</v>
       </c>
       <c r="N2">
-        <v>0.6354829111055176</v>
+        <v>0.6354829111055177</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>0.6354829111020791</v>
+        <v>0.6354829111020779</v>
       </c>
       <c r="Q2">
-        <v>-0.003601422288891855</v>
+        <v>-0.003601422289012236</v>
       </c>
       <c r="R2">
         <v>0</v>
       </c>
       <c r="S2">
-        <v>179.9963985778739</v>
+        <v>179.9963985778737</v>
       </c>
       <c r="T2">
-        <v>2.883136987405561</v>
+        <v>2.883136987405559</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -9437,22 +9437,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.6354829110747874</v>
+        <v>0.6354829110747872</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.6354829111962885</v>
+        <v>0.635482911196287</v>
       </c>
       <c r="Q3">
-        <v>-0.003601414077308141</v>
+        <v>-0.003601414077433403</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
       <c r="S3">
-        <v>179.9963985761586</v>
+        <v>179.9963985761584</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -9460,7 +9460,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -9499,22 +9499,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.6354829110779606</v>
+        <v>0.6354829110779604</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.635482911237765</v>
+        <v>0.6354829112377636</v>
       </c>
       <c r="Q4">
-        <v>-0.003601409590438953</v>
+        <v>-0.003601409590569241</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.9963985736636</v>
+        <v>179.9963985736634</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -9522,7 +9522,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -9561,22 +9561,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.6354829110779607</v>
+        <v>0.6354829110779604</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.6354829112377653</v>
+        <v>0.6354829112377636</v>
       </c>
       <c r="Q5">
-        <v>-0.003601409590439661</v>
+        <v>-0.003601409590587577</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9963985736636</v>
+        <v>179.9963985736634</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -9584,7 +9584,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -9623,22 +9623,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.6354829110779607</v>
+        <v>0.6354829110779604</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.6354829112377653</v>
+        <v>0.6354829112377638</v>
       </c>
       <c r="Q6">
-        <v>-0.003601409590439323</v>
+        <v>-0.003601409590572478</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>179.9963985736636</v>
+        <v>179.9963985736634</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -9646,7 +9646,7 @@
     </row>
     <row r="7" spans="1:20">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -9685,22 +9685,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.6354829109051782</v>
+        <v>0.6354829109051779</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>0.6354829114317636</v>
+        <v>0.6354829114317622</v>
       </c>
       <c r="Q7">
-        <v>-0.003601398395214257</v>
+        <v>-0.003601398395350318</v>
       </c>
       <c r="R7">
         <v>0</v>
       </c>
       <c r="S7">
-        <v>179.9963985815373</v>
+        <v>179.9963985815371</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -9708,7 +9708,7 @@
     </row>
     <row r="8" spans="1:20">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -9747,22 +9747,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.6354829109051784</v>
+        <v>0.6354829109051779</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>0.6354829114317639</v>
+        <v>0.6354829114317622</v>
       </c>
       <c r="Q8">
-        <v>-0.003601398395226525</v>
+        <v>-0.003601398395368658</v>
       </c>
       <c r="R8">
         <v>0</v>
       </c>
       <c r="S8">
-        <v>179.9963985815373</v>
+        <v>179.9963985815371</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -9770,7 +9770,7 @@
     </row>
     <row r="9" spans="1:20">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -9809,22 +9809,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.6354829109051784</v>
+        <v>0.6354829109051782</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>0.6354829114317639</v>
+        <v>0.6354829114317624</v>
       </c>
       <c r="Q9">
-        <v>-0.003601398395226186</v>
+        <v>-0.003601398395359338</v>
       </c>
       <c r="R9">
         <v>0</v>
       </c>
       <c r="S9">
-        <v>179.9963985815373</v>
+        <v>179.9963985815371</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -9904,69 +9904,69 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>2.886005588710062</v>
+        <v>2.886005588710051</v>
       </c>
       <c r="D2">
-        <v>2.885691010138483</v>
+        <v>2.885691010138484</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>33.32472207049037</v>
+        <v>33.32472207049025</v>
       </c>
       <c r="G2">
-        <v>33.32108963003072</v>
+        <v>33.32108963003073</v>
       </c>
       <c r="H2">
-        <v>0.4394678541080421</v>
+        <v>0.4394678541080371</v>
       </c>
       <c r="I2">
-        <v>4.386313816163394</v>
+        <v>4.386313816163414</v>
       </c>
       <c r="J2">
-        <v>0.437816359016784</v>
+        <v>0.4378163590167802</v>
       </c>
       <c r="K2">
-        <v>4.378163482112572</v>
+        <v>4.378163482112585</v>
       </c>
       <c r="L2">
-        <v>0.4378163589897157</v>
+        <v>0.4378163589897112</v>
       </c>
       <c r="M2">
-        <v>4.378163482065464</v>
+        <v>4.378163482065474</v>
       </c>
       <c r="N2">
-        <v>0.6354829111055176</v>
+        <v>0.6354829111055184</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>0.6354829111020789</v>
+        <v>0.6354829111020774</v>
       </c>
       <c r="Q2">
-        <v>-0.00360142228906818</v>
+        <v>-0.003601422289080287</v>
       </c>
       <c r="R2">
         <v>0</v>
       </c>
       <c r="S2">
-        <v>179.9963985778739</v>
+        <v>179.9963985778734</v>
       </c>
       <c r="T2">
-        <v>2.883136987405548</v>
+        <v>2.883136987405569</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -10005,22 +10005,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.635482911074787</v>
+        <v>0.6354829110747877</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.6354829111962879</v>
+        <v>0.6354829111962867</v>
       </c>
       <c r="Q3">
-        <v>-0.003601414077476226</v>
+        <v>-0.00360141407752457</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
       <c r="S3">
-        <v>179.9963985761586</v>
+        <v>179.996398576158</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -10028,7 +10028,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -10067,22 +10067,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.6354829110779604</v>
+        <v>0.6354829110779607</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.6354829112377646</v>
+        <v>0.6354829112377633</v>
       </c>
       <c r="Q4">
-        <v>-0.00360140959061313</v>
+        <v>-0.003601409590649519</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.9963985736636</v>
+        <v>179.996398573663</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -10090,7 +10090,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -10129,22 +10129,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.6354829110779603</v>
+        <v>0.635482911077961</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.6354829112377642</v>
+        <v>0.6354829112377632</v>
       </c>
       <c r="Q5">
-        <v>-0.003601409590613187</v>
+        <v>-0.003601409590678696</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9963985736636</v>
+        <v>179.996398573663</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -10152,7 +10152,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -10191,22 +10191,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.6354829110779603</v>
+        <v>0.6354829110779607</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.6354829112377646</v>
+        <v>0.6354829112377631</v>
       </c>
       <c r="Q6">
-        <v>-0.003601409590613175</v>
+        <v>-0.003601409590666241</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>179.9963985736636</v>
+        <v>179.996398573663</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -10214,7 +10214,7 @@
     </row>
     <row r="7" spans="1:20">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -10253,22 +10253,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.6354829108969501</v>
+        <v>0.6354829108969505</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>0.6354829114410009</v>
+        <v>0.6354829114409999</v>
       </c>
       <c r="Q7">
-        <v>-0.003601397862284689</v>
+        <v>-0.003601397862332633</v>
       </c>
       <c r="R7">
         <v>0</v>
       </c>
       <c r="S7">
-        <v>179.9963985819122</v>
+        <v>179.9963985819117</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -10276,7 +10276,7 @@
     </row>
     <row r="8" spans="1:20">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -10315,22 +10315,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.6354829108969501</v>
+        <v>0.6354829108969506</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>0.6354829114410011</v>
+        <v>0.6354829114409998</v>
       </c>
       <c r="Q8">
-        <v>-0.003601397862278966</v>
+        <v>-0.003601397862361816</v>
       </c>
       <c r="R8">
         <v>0</v>
       </c>
       <c r="S8">
-        <v>179.9963985819122</v>
+        <v>179.9963985819117</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -10338,7 +10338,7 @@
     </row>
     <row r="9" spans="1:20">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -10377,22 +10377,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.6354829108969501</v>
+        <v>0.6354829108969505</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>0.6354829114410011</v>
+        <v>0.6354829114409998</v>
       </c>
       <c r="Q9">
-        <v>-0.003601397862278958</v>
+        <v>-0.003601397862349361</v>
       </c>
       <c r="R9">
         <v>0</v>
       </c>
       <c r="S9">
-        <v>179.9963985819122</v>
+        <v>179.9963985819117</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -10472,13 +10472,13 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>1.171448579576277</v>
+        <v>1.171448579576276</v>
       </c>
       <c r="D2">
         <v>1.17161440147702</v>
@@ -10487,46 +10487,46 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>13.52672305520337</v>
+        <v>13.52672305520335</v>
       </c>
       <c r="G2">
         <v>13.528637801584</v>
       </c>
       <c r="H2">
-        <v>0.4394678541080287</v>
+        <v>0.4394678541080367</v>
       </c>
       <c r="I2">
-        <v>4.386313816163398</v>
+        <v>4.386313816163413</v>
       </c>
       <c r="J2">
-        <v>0.4378163590167708</v>
+        <v>0.4378163590167795</v>
       </c>
       <c r="K2">
-        <v>4.378163482112574</v>
+        <v>4.378163482112584</v>
       </c>
       <c r="L2">
-        <v>0.4378163589897015</v>
+        <v>0.4378163589897109</v>
       </c>
       <c r="M2">
-        <v>4.378163482065465</v>
+        <v>4.378163482065473</v>
       </c>
       <c r="N2">
-        <v>0.9728378693346232</v>
+        <v>0.9728378693346221</v>
       </c>
       <c r="O2">
-        <v>0.7175004542318558</v>
+        <v>0.7175004542318563</v>
       </c>
       <c r="P2">
-        <v>0.8438603770761439</v>
+        <v>0.8438603770761443</v>
       </c>
       <c r="Q2">
-        <v>17.5599575626366</v>
+        <v>17.55995756263659</v>
       </c>
       <c r="R2">
-        <v>-104.8932091336501</v>
+        <v>-104.89320913365</v>
       </c>
       <c r="S2">
-        <v>151.7135605277527</v>
+        <v>151.7135605277526</v>
       </c>
       <c r="T2">
         <v>1.171105864596103</v>
@@ -10534,7 +10534,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -10573,22 +10573,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9728378693178543</v>
+        <v>0.9728378693178532</v>
       </c>
       <c r="O3">
-        <v>0.717500454234335</v>
+        <v>0.7175004542343357</v>
       </c>
       <c r="P3">
-        <v>0.8438603771054701</v>
+        <v>0.8438603771054703</v>
       </c>
       <c r="Q3">
-        <v>17.55995756471143</v>
+        <v>17.55995756471142</v>
       </c>
       <c r="R3">
-        <v>-104.8932091282562</v>
+        <v>-104.8932091282561</v>
       </c>
       <c r="S3">
-        <v>151.7135605295005</v>
+        <v>151.7135605295004</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -10596,7 +10596,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -10635,16 +10635,16 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9728378693167383</v>
+        <v>0.9728378693167371</v>
       </c>
       <c r="O4">
-        <v>0.7175004542488181</v>
+        <v>0.7175004542488189</v>
       </c>
       <c r="P4">
-        <v>0.8438603771246129</v>
+        <v>0.8438603771246131</v>
       </c>
       <c r="Q4">
-        <v>17.55995756590171</v>
+        <v>17.5599575659017</v>
       </c>
       <c r="R4">
         <v>-104.8932091257061</v>
@@ -10658,7 +10658,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -10697,19 +10697,19 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9728378693167383</v>
+        <v>0.972837869316737</v>
       </c>
       <c r="O5">
-        <v>0.7175004542488183</v>
+        <v>0.7175004542488188</v>
       </c>
       <c r="P5">
-        <v>0.8438603771246129</v>
+        <v>0.8438603771246135</v>
       </c>
       <c r="Q5">
-        <v>17.55995756590172</v>
+        <v>17.5599575659017</v>
       </c>
       <c r="R5">
-        <v>-104.8932091257061</v>
+        <v>-104.893209125706</v>
       </c>
       <c r="S5">
         <v>151.7135605299476</v>
@@ -10720,7 +10720,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -10759,16 +10759,16 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.9728378693167383</v>
+        <v>0.9728378693167371</v>
       </c>
       <c r="O6">
-        <v>0.7175004542488183</v>
+        <v>0.7175004542488189</v>
       </c>
       <c r="P6">
-        <v>0.843860377124613</v>
+        <v>0.8438603771246133</v>
       </c>
       <c r="Q6">
-        <v>17.55995756590172</v>
+        <v>17.5599575659017</v>
       </c>
       <c r="R6">
         <v>-104.8932091257061</v>
@@ -10782,7 +10782,7 @@
     </row>
     <row r="7" spans="1:20">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -10821,22 +10821,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.9728378692411234</v>
+        <v>0.9728378692411221</v>
       </c>
       <c r="O7">
-        <v>0.717500454166129</v>
+        <v>0.7175004541661297</v>
       </c>
       <c r="P7">
-        <v>0.8438603771441477</v>
+        <v>0.8438603771441481</v>
       </c>
       <c r="Q7">
-        <v>17.55995756835943</v>
+        <v>17.55995756835941</v>
       </c>
       <c r="R7">
-        <v>-104.8932091157489</v>
+        <v>-104.8932091157488</v>
       </c>
       <c r="S7">
-        <v>151.7135605356605</v>
+        <v>151.7135605356604</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -10844,7 +10844,7 @@
     </row>
     <row r="8" spans="1:20">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -10883,22 +10883,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.9728378692411234</v>
+        <v>0.9728378692411224</v>
       </c>
       <c r="O8">
-        <v>0.7175004541661292</v>
+        <v>0.7175004541661298</v>
       </c>
       <c r="P8">
-        <v>0.843860377144148</v>
+        <v>0.8438603771441483</v>
       </c>
       <c r="Q8">
-        <v>17.55995756835943</v>
+        <v>17.55995756835941</v>
       </c>
       <c r="R8">
-        <v>-104.8932091157489</v>
+        <v>-104.8932091157488</v>
       </c>
       <c r="S8">
-        <v>151.7135605356605</v>
+        <v>151.7135605356604</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -10906,7 +10906,7 @@
     </row>
     <row r="9" spans="1:20">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -10945,22 +10945,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.9728378692411234</v>
+        <v>0.9728378692411224</v>
       </c>
       <c r="O9">
-        <v>0.7175004541661292</v>
+        <v>0.7175004541661297</v>
       </c>
       <c r="P9">
-        <v>0.843860377144148</v>
+        <v>0.8438603771441482</v>
       </c>
       <c r="Q9">
-        <v>17.55995756835943</v>
+        <v>17.55995756835941</v>
       </c>
       <c r="R9">
-        <v>-104.8932091157489</v>
+        <v>-104.8932091157488</v>
       </c>
       <c r="S9">
-        <v>151.7135605356605</v>
+        <v>151.7135605356604</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -11040,69 +11040,69 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>1.171448579576277</v>
+        <v>1.171448579576276</v>
       </c>
       <c r="D2">
-        <v>1.17161440147702</v>
+        <v>1.171614401477019</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>13.52672305520336</v>
+        <v>13.52672305520335</v>
       </c>
       <c r="G2">
-        <v>13.528637801584</v>
+        <v>13.52863780158398</v>
       </c>
       <c r="H2">
-        <v>0.4394678541080421</v>
+        <v>0.4394678541080371</v>
       </c>
       <c r="I2">
-        <v>4.386313816163394</v>
+        <v>4.386313816163414</v>
       </c>
       <c r="J2">
-        <v>0.437816359016784</v>
+        <v>0.4378163590167802</v>
       </c>
       <c r="K2">
-        <v>4.378163482112572</v>
+        <v>4.378163482112585</v>
       </c>
       <c r="L2">
-        <v>0.4378163589897157</v>
+        <v>0.4378163589897112</v>
       </c>
       <c r="M2">
-        <v>4.378163482065464</v>
+        <v>4.378163482065474</v>
       </c>
       <c r="N2">
-        <v>0.9728378693346229</v>
+        <v>0.972837869334622</v>
       </c>
       <c r="O2">
-        <v>0.7175004542318563</v>
+        <v>0.7175004542318575</v>
       </c>
       <c r="P2">
-        <v>0.8438603770761436</v>
+        <v>0.8438603770761447</v>
       </c>
       <c r="Q2">
-        <v>17.55995756263662</v>
+        <v>17.55995756263657</v>
       </c>
       <c r="R2">
         <v>-104.89320913365</v>
       </c>
       <c r="S2">
-        <v>151.7135605277526</v>
+        <v>151.7135605277525</v>
       </c>
       <c r="T2">
-        <v>1.171105864596101</v>
+        <v>1.171105864596104</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -11141,22 +11141,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9728378693178538</v>
+        <v>0.9728378693178532</v>
       </c>
       <c r="O3">
-        <v>0.7175004542343354</v>
+        <v>0.7175004542343368</v>
       </c>
       <c r="P3">
-        <v>0.8438603771054697</v>
+        <v>0.8438603771054709</v>
       </c>
       <c r="Q3">
-        <v>17.55995756471144</v>
+        <v>17.55995756471139</v>
       </c>
       <c r="R3">
-        <v>-104.8932091282562</v>
+        <v>-104.8932091282561</v>
       </c>
       <c r="S3">
-        <v>151.7135605295005</v>
+        <v>151.7135605295003</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -11164,7 +11164,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -11203,22 +11203,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9728378693167377</v>
+        <v>0.9728378693167369</v>
       </c>
       <c r="O4">
-        <v>0.7175004542488186</v>
+        <v>0.71750045424882</v>
       </c>
       <c r="P4">
-        <v>0.8438603771246127</v>
+        <v>0.8438603771246137</v>
       </c>
       <c r="Q4">
-        <v>17.55995756590173</v>
+        <v>17.55995756590168</v>
       </c>
       <c r="R4">
-        <v>-104.8932091257061</v>
+        <v>-104.893209125706</v>
       </c>
       <c r="S4">
-        <v>151.7135605299476</v>
+        <v>151.7135605299474</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -11226,7 +11226,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -11265,22 +11265,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9728378693167377</v>
+        <v>0.972837869316737</v>
       </c>
       <c r="O5">
-        <v>0.7175004542488186</v>
+        <v>0.71750045424882</v>
       </c>
       <c r="P5">
-        <v>0.8438603771246127</v>
+        <v>0.8438603771246137</v>
       </c>
       <c r="Q5">
-        <v>17.55995756590173</v>
+        <v>17.55995756590168</v>
       </c>
       <c r="R5">
         <v>-104.8932091257061</v>
       </c>
       <c r="S5">
-        <v>151.7135605299476</v>
+        <v>151.7135605299474</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -11288,7 +11288,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -11327,22 +11327,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.9728378693167377</v>
+        <v>0.972837869316737</v>
       </c>
       <c r="O6">
-        <v>0.7175004542488186</v>
+        <v>0.71750045424882</v>
       </c>
       <c r="P6">
-        <v>0.8438603771246126</v>
+        <v>0.8438603771246137</v>
       </c>
       <c r="Q6">
-        <v>17.55995756590173</v>
+        <v>17.55995756590168</v>
       </c>
       <c r="R6">
         <v>-104.8932091257061</v>
       </c>
       <c r="S6">
-        <v>151.7135605299476</v>
+        <v>151.7135605299474</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -11350,7 +11350,7 @@
     </row>
     <row r="7" spans="1:20">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -11389,22 +11389,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.9728378692375222</v>
+        <v>0.9728378692375214</v>
       </c>
       <c r="O7">
-        <v>0.717500454162192</v>
+        <v>0.7175004541621932</v>
       </c>
       <c r="P7">
-        <v>0.8438603771450776</v>
+        <v>0.8438603771450788</v>
       </c>
       <c r="Q7">
-        <v>17.55995756847648</v>
+        <v>17.55995756847643</v>
       </c>
       <c r="R7">
         <v>-104.8932091152747</v>
       </c>
       <c r="S7">
-        <v>151.7135605359325</v>
+        <v>151.7135605359323</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -11412,7 +11412,7 @@
     </row>
     <row r="8" spans="1:20">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -11451,22 +11451,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.9728378692375222</v>
+        <v>0.9728378692375215</v>
       </c>
       <c r="O8">
-        <v>0.7175004541621921</v>
+        <v>0.7175004541621934</v>
       </c>
       <c r="P8">
-        <v>0.8438603771450776</v>
+        <v>0.8438603771450788</v>
       </c>
       <c r="Q8">
-        <v>17.55995756847648</v>
+        <v>17.55995756847642</v>
       </c>
       <c r="R8">
         <v>-104.8932091152747</v>
       </c>
       <c r="S8">
-        <v>151.7135605359325</v>
+        <v>151.7135605359323</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -11474,7 +11474,7 @@
     </row>
     <row r="9" spans="1:20">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -11513,22 +11513,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.9728378692375222</v>
+        <v>0.9728378692375214</v>
       </c>
       <c r="O9">
-        <v>0.7175004541621921</v>
+        <v>0.7175004541621934</v>
       </c>
       <c r="P9">
-        <v>0.8438603771450776</v>
+        <v>0.8438603771450787</v>
       </c>
       <c r="Q9">
-        <v>17.55995756847648</v>
+        <v>17.55995756847643</v>
       </c>
       <c r="R9">
         <v>-104.8932091152747</v>
       </c>
       <c r="S9">
-        <v>151.7135605359325</v>
+        <v>151.7135605359323</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -11608,69 +11608,69 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>2.308723611495856</v>
+        <v>2.308723611495858</v>
       </c>
       <c r="D2">
-        <v>2.308436531756416</v>
+        <v>2.308436531756417</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>26.65884397163155</v>
+        <v>26.65884397163157</v>
       </c>
       <c r="G2">
-        <v>26.65552906033465</v>
+        <v>26.65552906033467</v>
       </c>
       <c r="H2">
-        <v>0.499655865049651</v>
+        <v>0.4996558650496533</v>
       </c>
       <c r="I2">
-        <v>4.985712340298376</v>
+        <v>4.985712340298373</v>
       </c>
       <c r="J2">
-        <v>0.497518590390245</v>
+        <v>0.4975185903902516</v>
       </c>
       <c r="K2">
-        <v>4.975185774913276</v>
+        <v>4.975185774913275</v>
       </c>
       <c r="L2">
-        <v>0.4975185904079639</v>
+        <v>0.4975185904079694</v>
       </c>
       <c r="M2">
-        <v>4.975185774943705</v>
+        <v>4.975185774943702</v>
       </c>
       <c r="N2">
-        <v>0.5777610338109186</v>
+        <v>0.5777610338109171</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>0.5777610338113891</v>
+        <v>0.5777610338113879</v>
       </c>
       <c r="Q2">
-        <v>-0.004107729544010559</v>
+        <v>-0.004107729544118554</v>
       </c>
       <c r="R2">
         <v>0</v>
       </c>
       <c r="S2">
-        <v>179.9958922701763</v>
+        <v>179.9958922701761</v>
       </c>
       <c r="T2">
-        <v>2.306115076548379</v>
+        <v>2.306115076548372</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -11709,16 +11709,16 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.5777610338095193</v>
+        <v>0.5777610338095175</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.5777610339235786</v>
+        <v>0.5777610339235768</v>
       </c>
       <c r="Q3">
-        <v>-0.004107716766785017</v>
+        <v>-0.004107716766862979</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -11732,7 +11732,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -11771,22 +11771,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.5777610338310679</v>
+        <v>0.5777610338310661</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.5777610339799542</v>
+        <v>0.5777610339799519</v>
       </c>
       <c r="Q4">
-        <v>-0.004107709068568712</v>
+        <v>-0.004107709068630546</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.9958922581889</v>
+        <v>179.9958922581888</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -11794,7 +11794,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -11833,22 +11833,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.577761033831068</v>
+        <v>0.5777610338310661</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.5777610339799542</v>
+        <v>0.577761033979952</v>
       </c>
       <c r="Q5">
-        <v>-0.004107709068567221</v>
+        <v>-0.004107709068624692</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9958922581889</v>
+        <v>179.9958922581888</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -11856,7 +11856,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -11895,22 +11895,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.577761033831068</v>
+        <v>0.5777610338310661</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.5777610339799542</v>
+        <v>0.5777610339799519</v>
       </c>
       <c r="Q6">
-        <v>-0.004107709068567065</v>
+        <v>-0.004107709068635008</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>179.9958922581889</v>
+        <v>179.9958922581888</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -11918,7 +11918,7 @@
     </row>
     <row r="7" spans="1:20">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -11957,22 +11957,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.5777610336660741</v>
+        <v>0.5777610336660723</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>0.5777610341651982</v>
+        <v>0.5777610341651961</v>
       </c>
       <c r="Q7">
-        <v>-0.004107697312133787</v>
+        <v>-0.004107697312176552</v>
       </c>
       <c r="R7">
         <v>0</v>
       </c>
       <c r="S7">
-        <v>179.9958922664571</v>
+        <v>179.995892266457</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -11980,7 +11980,7 @@
     </row>
     <row r="8" spans="1:20">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -12019,22 +12019,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.5777610336660743</v>
+        <v>0.5777610336660723</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>0.5777610341651982</v>
+        <v>0.5777610341651961</v>
       </c>
       <c r="Q8">
-        <v>-0.004107697312125946</v>
+        <v>-0.004107697312177067</v>
       </c>
       <c r="R8">
         <v>0</v>
       </c>
       <c r="S8">
-        <v>179.9958922664571</v>
+        <v>179.995892266457</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -12042,7 +12042,7 @@
     </row>
     <row r="9" spans="1:20">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -12081,22 +12081,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.5777610336660743</v>
+        <v>0.5777610336660723</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>0.5777610341651983</v>
+        <v>0.5777610341651961</v>
       </c>
       <c r="Q9">
-        <v>-0.004107697312125785</v>
+        <v>-0.004107697312187384</v>
       </c>
       <c r="R9">
         <v>0</v>
       </c>
       <c r="S9">
-        <v>179.9958922664571</v>
+        <v>179.995892266457</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -12137,7 +12137,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>1.171673335390808</v>
@@ -12160,7 +12160,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -12183,7 +12183,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -12206,7 +12206,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -12229,7 +12229,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -12252,7 +12252,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -12275,7 +12275,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -12298,7 +12298,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -12393,69 +12393,69 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>2.308723611495856</v>
+        <v>2.308723611495858</v>
       </c>
       <c r="D2">
-        <v>2.308436531756416</v>
+        <v>2.308436531756417</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>26.65884397163155</v>
+        <v>26.65884397163157</v>
       </c>
       <c r="G2">
-        <v>26.65552906033465</v>
+        <v>26.65552906033467</v>
       </c>
       <c r="H2">
-        <v>0.499655865049651</v>
+        <v>0.4996558650496533</v>
       </c>
       <c r="I2">
-        <v>4.985712340298376</v>
+        <v>4.985712340298373</v>
       </c>
       <c r="J2">
-        <v>0.497518590390245</v>
+        <v>0.4975185903902516</v>
       </c>
       <c r="K2">
-        <v>4.975185774913276</v>
+        <v>4.975185774913275</v>
       </c>
       <c r="L2">
-        <v>0.4975185904079639</v>
+        <v>0.4975185904079694</v>
       </c>
       <c r="M2">
-        <v>4.975185774943705</v>
+        <v>4.975185774943702</v>
       </c>
       <c r="N2">
-        <v>0.5777610338109186</v>
+        <v>0.5777610338109171</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>0.5777610338113891</v>
+        <v>0.5777610338113879</v>
       </c>
       <c r="Q2">
-        <v>-0.004107729544010559</v>
+        <v>-0.004107729544118554</v>
       </c>
       <c r="R2">
         <v>0</v>
       </c>
       <c r="S2">
-        <v>179.9958922701763</v>
+        <v>179.9958922701761</v>
       </c>
       <c r="T2">
-        <v>2.306115076548379</v>
+        <v>2.306115076548372</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -12494,16 +12494,16 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.5777610338095193</v>
+        <v>0.5777610338095175</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.5777610339235786</v>
+        <v>0.5777610339235768</v>
       </c>
       <c r="Q3">
-        <v>-0.004107716766785017</v>
+        <v>-0.004107716766862979</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -12517,7 +12517,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -12556,22 +12556,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.5777610338310679</v>
+        <v>0.5777610338310661</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.5777610339799542</v>
+        <v>0.5777610339799519</v>
       </c>
       <c r="Q4">
-        <v>-0.004107709068568712</v>
+        <v>-0.004107709068630546</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.9958922581889</v>
+        <v>179.9958922581888</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -12579,7 +12579,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -12618,22 +12618,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.577761033831068</v>
+        <v>0.5777610338310661</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.5777610339799542</v>
+        <v>0.577761033979952</v>
       </c>
       <c r="Q5">
-        <v>-0.004107709068567221</v>
+        <v>-0.004107709068624692</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9958922581889</v>
+        <v>179.9958922581888</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -12641,7 +12641,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -12680,22 +12680,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.577761033831068</v>
+        <v>0.5777610338310661</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.5777610339799542</v>
+        <v>0.5777610339799519</v>
       </c>
       <c r="Q6">
-        <v>-0.004107709068567065</v>
+        <v>-0.004107709068635008</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>179.9958922581889</v>
+        <v>179.9958922581888</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -12703,7 +12703,7 @@
     </row>
     <row r="7" spans="1:20">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -12742,22 +12742,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.5777610336660741</v>
+        <v>0.5777610336660723</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>0.5777610341651982</v>
+        <v>0.5777610341651961</v>
       </c>
       <c r="Q7">
-        <v>-0.004107697312133787</v>
+        <v>-0.004107697312176552</v>
       </c>
       <c r="R7">
         <v>0</v>
       </c>
       <c r="S7">
-        <v>179.9958922664571</v>
+        <v>179.995892266457</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -12765,7 +12765,7 @@
     </row>
     <row r="8" spans="1:20">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -12804,22 +12804,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.5777610336660743</v>
+        <v>0.5777610336660723</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>0.5777610341651982</v>
+        <v>0.5777610341651961</v>
       </c>
       <c r="Q8">
-        <v>-0.004107697312125946</v>
+        <v>-0.004107697312177067</v>
       </c>
       <c r="R8">
         <v>0</v>
       </c>
       <c r="S8">
-        <v>179.9958922664571</v>
+        <v>179.995892266457</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -12827,7 +12827,7 @@
     </row>
     <row r="9" spans="1:20">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -12866,22 +12866,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.5777610336660743</v>
+        <v>0.5777610336660723</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>0.5777610341651983</v>
+        <v>0.5777610341651961</v>
       </c>
       <c r="Q9">
-        <v>-0.004107697312125785</v>
+        <v>-0.004107697312187384</v>
       </c>
       <c r="R9">
         <v>0</v>
       </c>
       <c r="S9">
-        <v>179.9958922664571</v>
+        <v>179.995892266457</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -12961,7 +12961,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -12970,7 +12970,7 @@
         <v>1.013569934881262</v>
       </c>
       <c r="D2">
-        <v>1.013734674375882</v>
+        <v>1.013734674375883</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -12979,51 +12979,51 @@
         <v>11.70369749492416</v>
       </c>
       <c r="G2">
-        <v>11.70559974275546</v>
+        <v>11.70559974275547</v>
       </c>
       <c r="H2">
-        <v>0.499655865049651</v>
+        <v>0.4996558650496533</v>
       </c>
       <c r="I2">
-        <v>4.985712340298376</v>
+        <v>4.985712340298373</v>
       </c>
       <c r="J2">
-        <v>0.497518590390245</v>
+        <v>0.4975185903902516</v>
       </c>
       <c r="K2">
-        <v>4.975185774913276</v>
+        <v>4.975185774913275</v>
       </c>
       <c r="L2">
-        <v>0.4975185904079639</v>
+        <v>0.4975185904079694</v>
       </c>
       <c r="M2">
-        <v>4.975185774943705</v>
+        <v>4.975185774943702</v>
       </c>
       <c r="N2">
-        <v>0.8719861190326098</v>
+        <v>0.8719861190326093</v>
       </c>
       <c r="O2">
-        <v>0.6208257824645782</v>
+        <v>0.6208257824645791</v>
       </c>
       <c r="P2">
-        <v>0.748998392334042</v>
+        <v>0.7489983923340414</v>
       </c>
       <c r="Q2">
-        <v>16.55159106704788</v>
+        <v>16.55159106704789</v>
       </c>
       <c r="R2">
         <v>-106.1399873126024</v>
       </c>
       <c r="S2">
-        <v>152.3190012608093</v>
+        <v>152.3190012608092</v>
       </c>
       <c r="T2">
-        <v>1.013196322776287</v>
+        <v>1.013196322776286</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -13062,22 +13062,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8719861190255289</v>
+        <v>0.8719861190255284</v>
       </c>
       <c r="O3">
-        <v>0.6208257824983051</v>
+        <v>0.620825782498306</v>
       </c>
       <c r="P3">
-        <v>0.7489983923867206</v>
+        <v>0.7489983923867199</v>
       </c>
       <c r="Q3">
-        <v>16.55159107073557</v>
+        <v>16.55159107073558</v>
       </c>
       <c r="R3">
         <v>-106.1399873041104</v>
       </c>
       <c r="S3">
-        <v>152.319001262388</v>
+        <v>152.3190012623879</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -13085,7 +13085,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -13124,22 +13124,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8719861190310287</v>
+        <v>0.8719861190310281</v>
       </c>
       <c r="O4">
-        <v>0.6208257825345511</v>
+        <v>0.6208257825345523</v>
       </c>
       <c r="P4">
-        <v>0.7489983924219461</v>
+        <v>0.7489983924219454</v>
       </c>
       <c r="Q4">
-        <v>16.55159107303126</v>
+        <v>16.55159107303129</v>
       </c>
       <c r="R4">
         <v>-106.1399872995509</v>
       </c>
       <c r="S4">
-        <v>152.319001262636</v>
+        <v>152.3190012626359</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -13147,7 +13147,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -13186,16 +13186,16 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8719861190310287</v>
+        <v>0.8719861190310281</v>
       </c>
       <c r="O5">
-        <v>0.6208257825345511</v>
+        <v>0.6208257825345523</v>
       </c>
       <c r="P5">
-        <v>0.748998392421946</v>
+        <v>0.7489983924219454</v>
       </c>
       <c r="Q5">
-        <v>16.55159107303126</v>
+        <v>16.55159107303129</v>
       </c>
       <c r="R5">
         <v>-106.1399872995509</v>
@@ -13209,7 +13209,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -13248,22 +13248,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.8719861190310287</v>
+        <v>0.871986119031028</v>
       </c>
       <c r="O6">
-        <v>0.6208257825345511</v>
+        <v>0.6208257825345523</v>
       </c>
       <c r="P6">
-        <v>0.7489983924219461</v>
+        <v>0.7489983924219454</v>
       </c>
       <c r="Q6">
-        <v>16.55159107303126</v>
+        <v>16.55159107303128</v>
       </c>
       <c r="R6">
         <v>-106.1399872995509</v>
       </c>
       <c r="S6">
-        <v>152.319001262636</v>
+        <v>152.3190012626359</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -13271,7 +13271,7 @@
     </row>
     <row r="7" spans="1:20">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -13310,22 +13310,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.8719861189531154</v>
+        <v>0.8719861189531146</v>
       </c>
       <c r="O7">
-        <v>0.6208257824491503</v>
+        <v>0.6208257824491517</v>
       </c>
       <c r="P7">
-        <v>0.7489983924449241</v>
+        <v>0.7489983924449236</v>
       </c>
       <c r="Q7">
-        <v>16.55159107588414</v>
+        <v>16.55159107588416</v>
       </c>
       <c r="R7">
-        <v>-106.1399872876657</v>
+        <v>-106.1399872876658</v>
       </c>
       <c r="S7">
-        <v>152.3190012692299</v>
+        <v>152.3190012692297</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -13333,7 +13333,7 @@
     </row>
     <row r="8" spans="1:20">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -13372,22 +13372,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.8719861189531154</v>
+        <v>0.8719861189531148</v>
       </c>
       <c r="O8">
-        <v>0.6208257824491502</v>
+        <v>0.6208257824491514</v>
       </c>
       <c r="P8">
-        <v>0.7489983924449241</v>
+        <v>0.7489983924449236</v>
       </c>
       <c r="Q8">
-        <v>16.55159107588413</v>
+        <v>16.55159107588415</v>
       </c>
       <c r="R8">
-        <v>-106.1399872876657</v>
+        <v>-106.1399872876658</v>
       </c>
       <c r="S8">
-        <v>152.3190012692299</v>
+        <v>152.3190012692297</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -13395,7 +13395,7 @@
     </row>
     <row r="9" spans="1:20">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -13434,22 +13434,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.8719861189531154</v>
+        <v>0.8719861189531148</v>
       </c>
       <c r="O9">
-        <v>0.6208257824491502</v>
+        <v>0.6208257824491514</v>
       </c>
       <c r="P9">
-        <v>0.7489983924449241</v>
+        <v>0.7489983924449236</v>
       </c>
       <c r="Q9">
-        <v>16.55159107588413</v>
+        <v>16.55159107588415</v>
       </c>
       <c r="R9">
-        <v>-106.1399872876657</v>
+        <v>-106.1399872876658</v>
       </c>
       <c r="S9">
-        <v>152.3190012692299</v>
+        <v>152.3190012692297</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -13529,7 +13529,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -13538,7 +13538,7 @@
         <v>1.013569934881262</v>
       </c>
       <c r="D2">
-        <v>1.013734674375882</v>
+        <v>1.013734674375883</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -13547,51 +13547,51 @@
         <v>11.70369749492416</v>
       </c>
       <c r="G2">
-        <v>11.70559974275546</v>
+        <v>11.70559974275547</v>
       </c>
       <c r="H2">
-        <v>0.499655865049651</v>
+        <v>0.4996558650496533</v>
       </c>
       <c r="I2">
-        <v>4.985712340298376</v>
+        <v>4.985712340298373</v>
       </c>
       <c r="J2">
-        <v>0.497518590390245</v>
+        <v>0.4975185903902516</v>
       </c>
       <c r="K2">
-        <v>4.975185774913276</v>
+        <v>4.975185774913275</v>
       </c>
       <c r="L2">
-        <v>0.4975185904079639</v>
+        <v>0.4975185904079694</v>
       </c>
       <c r="M2">
-        <v>4.975185774943705</v>
+        <v>4.975185774943702</v>
       </c>
       <c r="N2">
-        <v>0.8719861190326098</v>
+        <v>0.8719861190326093</v>
       </c>
       <c r="O2">
-        <v>0.6208257824645782</v>
+        <v>0.6208257824645791</v>
       </c>
       <c r="P2">
-        <v>0.748998392334042</v>
+        <v>0.7489983923340414</v>
       </c>
       <c r="Q2">
-        <v>16.55159106704788</v>
+        <v>16.55159106704789</v>
       </c>
       <c r="R2">
         <v>-106.1399873126024</v>
       </c>
       <c r="S2">
-        <v>152.3190012608093</v>
+        <v>152.3190012608092</v>
       </c>
       <c r="T2">
-        <v>1.013196322776287</v>
+        <v>1.013196322776286</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -13630,22 +13630,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8719861190255289</v>
+        <v>0.8719861190255284</v>
       </c>
       <c r="O3">
-        <v>0.6208257824983051</v>
+        <v>0.620825782498306</v>
       </c>
       <c r="P3">
-        <v>0.7489983923867206</v>
+        <v>0.7489983923867199</v>
       </c>
       <c r="Q3">
-        <v>16.55159107073557</v>
+        <v>16.55159107073558</v>
       </c>
       <c r="R3">
         <v>-106.1399873041104</v>
       </c>
       <c r="S3">
-        <v>152.319001262388</v>
+        <v>152.3190012623879</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -13653,7 +13653,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -13692,22 +13692,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8719861190310287</v>
+        <v>0.8719861190310281</v>
       </c>
       <c r="O4">
-        <v>0.6208257825345511</v>
+        <v>0.6208257825345523</v>
       </c>
       <c r="P4">
-        <v>0.7489983924219461</v>
+        <v>0.7489983924219454</v>
       </c>
       <c r="Q4">
-        <v>16.55159107303126</v>
+        <v>16.55159107303129</v>
       </c>
       <c r="R4">
         <v>-106.1399872995509</v>
       </c>
       <c r="S4">
-        <v>152.319001262636</v>
+        <v>152.3190012626359</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -13715,7 +13715,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -13754,16 +13754,16 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8719861190310287</v>
+        <v>0.8719861190310281</v>
       </c>
       <c r="O5">
-        <v>0.6208257825345511</v>
+        <v>0.6208257825345523</v>
       </c>
       <c r="P5">
-        <v>0.748998392421946</v>
+        <v>0.7489983924219454</v>
       </c>
       <c r="Q5">
-        <v>16.55159107303126</v>
+        <v>16.55159107303129</v>
       </c>
       <c r="R5">
         <v>-106.1399872995509</v>
@@ -13777,7 +13777,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -13816,22 +13816,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.8719861190310287</v>
+        <v>0.871986119031028</v>
       </c>
       <c r="O6">
-        <v>0.6208257825345511</v>
+        <v>0.6208257825345523</v>
       </c>
       <c r="P6">
-        <v>0.7489983924219461</v>
+        <v>0.7489983924219454</v>
       </c>
       <c r="Q6">
-        <v>16.55159107303126</v>
+        <v>16.55159107303128</v>
       </c>
       <c r="R6">
         <v>-106.1399872995509</v>
       </c>
       <c r="S6">
-        <v>152.319001262636</v>
+        <v>152.3190012626359</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -13839,7 +13839,7 @@
     </row>
     <row r="7" spans="1:20">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -13878,22 +13878,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.8719861189531154</v>
+        <v>0.8719861189531146</v>
       </c>
       <c r="O7">
-        <v>0.6208257824491503</v>
+        <v>0.6208257824491517</v>
       </c>
       <c r="P7">
-        <v>0.7489983924449241</v>
+        <v>0.7489983924449236</v>
       </c>
       <c r="Q7">
-        <v>16.55159107588414</v>
+        <v>16.55159107588416</v>
       </c>
       <c r="R7">
-        <v>-106.1399872876657</v>
+        <v>-106.1399872876658</v>
       </c>
       <c r="S7">
-        <v>152.3190012692299</v>
+        <v>152.3190012692297</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -13901,7 +13901,7 @@
     </row>
     <row r="8" spans="1:20">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -13940,22 +13940,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.8719861189531154</v>
+        <v>0.8719861189531148</v>
       </c>
       <c r="O8">
-        <v>0.6208257824491502</v>
+        <v>0.6208257824491514</v>
       </c>
       <c r="P8">
-        <v>0.7489983924449241</v>
+        <v>0.7489983924449236</v>
       </c>
       <c r="Q8">
-        <v>16.55159107588413</v>
+        <v>16.55159107588415</v>
       </c>
       <c r="R8">
-        <v>-106.1399872876657</v>
+        <v>-106.1399872876658</v>
       </c>
       <c r="S8">
-        <v>152.3190012692299</v>
+        <v>152.3190012692297</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -13963,7 +13963,7 @@
     </row>
     <row r="9" spans="1:20">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -14002,22 +14002,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.8719861189531154</v>
+        <v>0.8719861189531148</v>
       </c>
       <c r="O9">
-        <v>0.6208257824491502</v>
+        <v>0.6208257824491514</v>
       </c>
       <c r="P9">
-        <v>0.7489983924449241</v>
+        <v>0.7489983924449236</v>
       </c>
       <c r="Q9">
-        <v>16.55159107588413</v>
+        <v>16.55159107588415</v>
       </c>
       <c r="R9">
-        <v>-106.1399872876657</v>
+        <v>-106.1399872876658</v>
       </c>
       <c r="S9">
-        <v>152.3190012692299</v>
+        <v>152.3190012692297</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -14058,7 +14058,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>1.171673335390808</v>
@@ -14081,7 +14081,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -14104,7 +14104,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -14127,7 +14127,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -14150,7 +14150,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -14173,7 +14173,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -14196,7 +14196,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -14219,7 +14219,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -14275,7 +14275,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>2.309401157911542</v>
@@ -14298,7 +14298,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -14321,7 +14321,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -14344,7 +14344,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -14367,7 +14367,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -14390,7 +14390,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -14413,7 +14413,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -14436,7 +14436,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -14492,7 +14492,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>2.309401157911542</v>
@@ -14515,7 +14515,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -14538,7 +14538,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -14561,7 +14561,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -14584,7 +14584,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -14607,7 +14607,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -14630,7 +14630,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -14653,7 +14653,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -14709,7 +14709,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>1.013804257465359</v>
@@ -14732,7 +14732,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -14755,7 +14755,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -14778,7 +14778,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -14801,7 +14801,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -14824,7 +14824,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -14847,7 +14847,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -14870,7 +14870,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -14926,7 +14926,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>1.013804257465359</v>
@@ -14949,7 +14949,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -14972,7 +14972,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -14995,7 +14995,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -15018,7 +15018,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -15041,7 +15041,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -15064,7 +15064,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -15087,7 +15087,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -15179,7 +15179,7 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -15200,45 +15200,45 @@
         <v>28.86751509915034</v>
       </c>
       <c r="H2">
-        <v>0.4394678541080287</v>
+        <v>0.4394678541080367</v>
       </c>
       <c r="I2">
-        <v>4.386313816163398</v>
+        <v>4.386313816163413</v>
       </c>
       <c r="J2">
-        <v>0.4378163590167708</v>
+        <v>0.4378163590167795</v>
       </c>
       <c r="K2">
-        <v>4.378163482112574</v>
+        <v>4.378163482112584</v>
       </c>
       <c r="L2">
-        <v>0.4378163589897015</v>
+        <v>0.4378163589897109</v>
       </c>
       <c r="M2">
-        <v>4.378163482065465</v>
+        <v>4.378163482065473</v>
       </c>
       <c r="N2">
-        <v>0.9526279648091457</v>
+        <v>0.9526279648091452</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>0.9526279648092955</v>
+        <v>0.9526279648092951</v>
       </c>
       <c r="Q2">
-        <v>-6.22627964230997E-13</v>
+        <v>-6.578216712955404E-13</v>
       </c>
       <c r="R2">
         <v>0</v>
       </c>
       <c r="S2">
-        <v>179.999999999992</v>
+        <v>179.9999999999919</v>
       </c>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -15277,27 +15277,27 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9526279647466794</v>
+        <v>0.9526279647466789</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.9526279648717616</v>
+        <v>0.9526279648717613</v>
       </c>
       <c r="Q3">
-        <v>3.310652522062277E-09</v>
+        <v>3.310626909119872E-09</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
       <c r="S3">
-        <v>179.9999999966807</v>
+        <v>179.9999999966806</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -15336,27 +15336,27 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9526279647275303</v>
+        <v>0.9526279647275299</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.9526279648909108</v>
+        <v>0.9526279648909106</v>
       </c>
       <c r="Q4">
-        <v>5.639473876233345E-09</v>
+        <v>5.639427528713096E-09</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.9999999943519</v>
+        <v>179.9999999943518</v>
       </c>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -15395,27 +15395,27 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9526279647275303</v>
+        <v>0.9526279647275299</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.9526279648909108</v>
+        <v>0.9526279648909104</v>
       </c>
       <c r="Q5">
-        <v>5.639473884589579E-09</v>
+        <v>5.639427677071936E-09</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9999999943519</v>
+        <v>179.9999999943518</v>
       </c>
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -15454,27 +15454,27 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.9526279647275303</v>
+        <v>0.9526279647275299</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.9526279648909108</v>
+        <v>0.9526279648909105</v>
       </c>
       <c r="Q6">
-        <v>5.639473885714179E-09</v>
+        <v>5.639431695047694E-09</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>179.9999999943519</v>
+        <v>179.9999999943518</v>
       </c>
     </row>
     <row r="7" spans="1:19">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -15513,16 +15513,16 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.9526279645441408</v>
+        <v>0.9526279645441403</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>0.9526279650743003</v>
+        <v>0.9526279650743</v>
       </c>
       <c r="Q7">
-        <v>6.748030165123181E-09</v>
+        <v>6.747979962385255E-09</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -15533,7 +15533,7 @@
     </row>
     <row r="8" spans="1:19">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -15572,27 +15572,27 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.952627964544141</v>
+        <v>0.9526279645441402</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>0.9526279650743003</v>
+        <v>0.9526279650742997</v>
       </c>
       <c r="Q8">
-        <v>6.748022463044082E-09</v>
+        <v>6.747980110744071E-09</v>
       </c>
       <c r="R8">
         <v>0</v>
       </c>
       <c r="S8">
-        <v>179.9999999932433</v>
+        <v>179.9999999932432</v>
       </c>
     </row>
     <row r="9" spans="1:19">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -15631,16 +15631,16 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.952627964544141</v>
+        <v>0.9526279645441404</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>0.9526279650743003</v>
+        <v>0.9526279650743</v>
       </c>
       <c r="Q9">
-        <v>6.748022464168682E-09</v>
+        <v>6.747984128719828E-09</v>
       </c>
       <c r="R9">
         <v>0</v>
